--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Misc\Time_Tracking\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453B2842-F496-49B4-9E45-79AFCBD82596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BFA9EA-974C-4FF2-B7C5-F2A163032DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4350" yWindow="1740" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="1485" yWindow="2400" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260209" sheetId="6" r:id="rId1"/>
-    <sheet name="20260202" sheetId="5" r:id="rId2"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId4"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId5"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId6"/>
+    <sheet name="20260302" sheetId="9" r:id="rId1"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId2"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId3"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId4"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId6"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId7"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId8"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="22">
   <si>
     <t>In</t>
   </si>
@@ -105,15 +108,120 @@
   <si>
     <t>Hours to 40</t>
   </si>
+  <si>
+    <t>Morning
+Hours</t>
+  </si>
+  <si>
+    <t>Afternoon
+Hours</t>
+  </si>
+  <si>
+    <t>Total
+Hours</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Time Off
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Holiday, Bereavement, etc.)</t>
+    </r>
+  </si>
+  <si>
+    <t>Daily Punch
+Count</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lunch
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Mins)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Over / Under
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Mins)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Out
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Lunch)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Lunch)</t>
+    </r>
+  </si>
+  <si>
+    <t>Hours &gt; 40</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +273,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -180,7 +304,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -309,12 +433,66 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -385,12 +563,27 @@
     <xf numFmtId="18" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="73">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -728,6 +921,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -738,6 +941,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -770,6 +983,287 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1068,319 +1562,384 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
-  <dimension ref="A1:L25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>02/09/2026</v>
+        <v>03/02/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (9th)</v>
+        <v>Mon (2nd)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C2" s="8">
-        <v>0.49861111111111112</v>
+        <v>0.55208333333333337</v>
       </c>
       <c r="D2" s="8">
-        <v>0.52916666666666667</v>
+        <v>0.57638888888888884</v>
       </c>
       <c r="E2" s="9">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>5.0500000000000007</v>
-      </c>
-      <c r="H2" s="11">
+        <v>6.3333333333333348</v>
+      </c>
+      <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>3.2999999999999989</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.35</v>
-      </c>
-      <c r="J2" s="13">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.5000000000000018</v>
+      </c>
+      <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>34.999999999999872</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-31.000000000000107</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (10th)</v>
+        <v>Tue (3rd)</v>
       </c>
       <c r="B3" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="C3" s="8">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53888888888888886</v>
+      </c>
       <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="H3" s="11">
+        <v>5.2666666666666666</v>
+      </c>
+      <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>16</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="J3" s="13" t="str">
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="K3" s="14" t="str">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (11th)</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="12">
+        <v>Wed (4th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J4" s="13" t="str">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="K4" s="14" t="str">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.4499999999999993</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.916666666666667</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (12th)</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
+        <v>Thu (5th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.48819444444444443</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.8000000000000007</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.549999999999998</v>
+      </c>
+      <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="K5" s="14" t="str">
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+        <v>44.000000000000085</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (13th)</v>
-      </c>
-      <c r="B6" s="8"/>
+        <v>Fri (6th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="13" t="str">
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I6" s="11">
         <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>9.0833333333333339</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="K6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
+      <c r="I7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>17.433333333333334</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>42.666666666666664</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>22.566666666666666</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-2.6666666666666643</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>2.6666666666666643</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="39" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1390,345 +1949,373 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
-  <dimension ref="A1:L25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>02/02/2026</v>
+        <v>02/23/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (2nd)</v>
+        <v>Mon (23rd)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C2" s="8">
-        <v>0.54722222222222228</v>
+        <v>0.52222222222222225</v>
       </c>
       <c r="D2" s="8">
-        <v>0.57638888888888884</v>
+        <v>0.55277777777777781</v>
       </c>
       <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="F2" s="30">
+        <f>COUNT(B2:E2)</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>6.2166666666666686</v>
-      </c>
-      <c r="H2" s="11">
+        <v>5.616666666666668</v>
+      </c>
+      <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>2.166666666666667</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3833333333333364</v>
-      </c>
-      <c r="J2" s="13">
+        <v>1.7333333333333325</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>7.3500000000000005</v>
+      </c>
+      <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>41.999999999999851</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-24.000000000000185</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>39.999999999999972</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (3rd)</v>
+        <v>Tue (24th)</v>
       </c>
       <c r="B3" s="8">
-        <v>0.29236111111111113</v>
+        <v>0.28819444444444442</v>
       </c>
       <c r="C3" s="8">
-        <v>0.55694444444444446</v>
+        <v>0.50069444444444444</v>
       </c>
       <c r="D3" s="8">
-        <v>0.58680555555555558</v>
+        <v>0.53125</v>
       </c>
       <c r="E3" s="9">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F5" si="0">COUNT(B3:E3)</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>6.35</v>
-      </c>
-      <c r="H3" s="11">
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>1.9166666666666652</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.2666666666666657</v>
-      </c>
-      <c r="J3" s="13">
+        <v>3.2499999999999991</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-16.999999999999943</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (4th)</v>
+        <v>Wed (25th)</v>
       </c>
       <c r="B4" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C4" s="8">
-        <v>0.54652777777777772</v>
+        <v>0.54236111111111107</v>
       </c>
       <c r="D4" s="8">
-        <v>0.57777777777777772</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="E4" s="9">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>6.1999999999999993</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.1333333333333337</v>
-      </c>
-      <c r="I4" s="12">
+      <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.1</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.25</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (5th)</v>
+        <v>Thu (26th)</v>
       </c>
       <c r="B5" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C5" s="8">
-        <v>0.48888888888888887</v>
+        <v>0.52013888888888893</v>
       </c>
       <c r="D5" s="8">
-        <v>0.51875000000000004</v>
+        <v>0.55069444444444449</v>
       </c>
       <c r="E5" s="9">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.5666666666666682</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>2.7833333333333314</v>
+      </c>
+      <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>4.8166666666666664</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.549999999999998</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666636</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000085</v>
-      </c>
-      <c r="K5" s="14">
+        <v>8.35</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v>-22.999999999999815</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (6th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.29166666666666669</v>
-      </c>
+        <v>Fri (27th)</v>
+      </c>
+      <c r="B6" s="27"/>
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
-      <c r="E6" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F6" s="11">
+      <c r="E6" s="31"/>
+      <c r="F6" s="30">
+        <f>IF(G6 = 8, 4, IF(G6 = 4, 2, COUNT(B6:E6)))</f>
         <v>4</v>
       </c>
       <c r="G6" s="10">
+        <v>8</v>
+      </c>
+      <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>-7</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="J6" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="K6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.349999999999994</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.3499999999999943</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-0.39999999999999858</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="34" priority="4" operator="greaterThan">
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="32" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1738,6 +2325,1150 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>02/16/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (16th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.58958333333333335</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>COUNT(B2:E2)</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>6.5000000000000009</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>1.8499999999999988</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (17th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.47708333333333336</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">COUNT(B3:E3)</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>4.533333333333335</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.8166666666666664</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3500000000000014</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.999999999999922</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-22.000000000000085</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (18th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.57222222222222219</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.2666666666666666</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (19th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53055555555555556</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.2666666666666657</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (20th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>2.333333333333333</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.75</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="56.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>02/09/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (9th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49861111111111112</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>COUNT(B2:E2)</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.0500000000000007</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.2999999999999989</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (10th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.49861111111111112</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">COUNT(B3:E3)</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.0500000000000007</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.2999999999999989</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (11th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56388888888888888</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.8666666666666671</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.4666666666666659</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (12th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53125</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.1333333333333337</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.2499999999999991</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.999999999999972</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (13th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.47986111111111113</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>4.6000000000000014</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.75</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3500000000000014</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>43.999999999999922</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-22.000000000000085</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.766666666666666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.7666666666666657</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="56.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>02/02/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (2nd)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>COUNT(B2:E2)</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>6.2166666666666686</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.166666666666667</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3833333333333364</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>41.999999999999851</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-24.000000000000185</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (3rd)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.29236111111111113</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F5" si="0">COUNT(B3:E3)</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.35</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.9166666666666652</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-16.999999999999943</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (4th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.57777777777777772</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.1999999999999993</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.1333333333333337</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (5th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.8166666666666664</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.549999999999998</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666636</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000085</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-22.999999999999815</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (6th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F6" s="30">
+        <f>COUNT(B6:E6)</f>
+        <v>2</v>
+      </c>
+      <c r="G6" s="11">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-7</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.349999999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.3499999999999943</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2087,7 +3818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2437,7 +4168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2787,7 +4518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BFA9EA-974C-4FF2-B7C5-F2A163032DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC9101C-A76F-41E0-BA10-E3F09F5EECB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="2400" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="3840" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260302" sheetId="9" r:id="rId1"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId2"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId3"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId4"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId6"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId7"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId8"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId9"/>
+    <sheet name="20260309" sheetId="10" r:id="rId1"/>
+    <sheet name="20260302" sheetId="9" r:id="rId2"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId3"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId4"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId5"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId6"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId7"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId8"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId9"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="22">
   <si>
     <t>In</t>
   </si>
@@ -583,7 +584,94 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="73">
+  <dxfs count="82">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1562,15 +1650,712 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>03/09/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (9th)</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="13" t="str">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (10th)</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="str">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (11th)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (12th)</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (13th)</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>40</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25" t="str">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4333333333333318</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.2833333333333332</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>3.466666666666665</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44.000000000000085</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6166666666666654</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.7999999999999972</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
@@ -1800,35 +2585,39 @@
       <c r="B6" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="8">
+        <v>0.45763888888888887</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.48819444444444443</v>
+      </c>
       <c r="E6" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>4.0666666666666664</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>4.2833333333333332</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K6" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
         <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
@@ -1838,7 +2627,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>42.666666666666664</v>
+        <v>41.93333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -1850,7 +2639,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>-2.6666666666666643</v>
+        <v>-1.93333333333333</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -1860,7 +2649,7 @@
       </c>
       <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>2.6666666666666643</v>
+        <v>1.93333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -1909,37 +2698,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1948,7 +2737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2285,37 +3074,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2324,7 +3113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2667,37 +3456,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2706,7 +3495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3049,37 +3838,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3088,7 +3877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3429,37 +4218,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3468,7 +4257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3787,29 +4576,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3818,7 +4607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4137,29 +4926,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4168,7 +4957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4487,379 +5276,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49375000000000002</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4333333333333318</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57152777777777775</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.2833333333333332</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52222222222222225</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>3.466666666666665</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44.000000000000085</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3999999999999986</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.6166666666666654</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.7999999999999972</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC9101C-A76F-41E0-BA10-E3F09F5EECB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221CC7E5-DA14-4FDA-BF58-2FDD9708F9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -654,6 +654,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -663,6 +673,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -674,6 +691,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -684,6 +721,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -870,53 +917,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1710,26 +1710,30 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Mon (9th)</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K2" s="13" t="str">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
@@ -1888,7 +1892,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -1900,7 +1904,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>40</v>
+        <v>30.916666666666664</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -1959,37 +1963,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2317,29 +2321,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2698,37 +2702,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3074,37 +3078,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3456,37 +3460,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3838,37 +3842,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4218,37 +4222,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4576,29 +4580,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="36" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4926,29 +4930,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="27" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5276,29 +5280,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="22" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="20" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221CC7E5-DA14-4FDA-BF58-2FDD9708F9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7696F93-5776-434A-A5EC-38930E2832A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -1713,35 +1713,39 @@
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="8">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.51527777777777772</v>
+      </c>
       <c r="E2" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>4.5833333333333339</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>16</v>
+        <v>3.6333333333333337</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K2" s="13" t="str">
+        <v>8.2166666666666686</v>
+      </c>
+      <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
+        <v>51.999999999999893</v>
+      </c>
+      <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-14.000000000000114</v>
       </c>
       <c r="M2" s="15"/>
     </row>
@@ -1750,26 +1754,30 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Tue (10th)</v>
       </c>
-      <c r="B3" s="8"/>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K3" s="13" t="str">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
@@ -1820,26 +1828,32 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (12th)</v>
       </c>
-      <c r="B5" s="8"/>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
+      <c r="E5" s="9">
+        <v>0.625</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="28"/>
+        <v>2</v>
+      </c>
+      <c r="G5" s="28">
+        <v>1</v>
+      </c>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
@@ -1892,7 +1906,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>9.0833333333333339</v>
+        <v>26.38333333333334</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -1904,7 +1918,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>30.916666666666664</v>
+        <v>13.61666666666666</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7696F93-5776-434A-A5EC-38930E2832A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A61724-6549-4F88-8E4B-22B34DE23C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -212,6 +212,31 @@
   </si>
   <si>
     <t>Hours &gt; 40</t>
+  </si>
+  <si>
+    <t>Pre-Lunch
+Hours</t>
+  </si>
+  <si>
+    <t>Post-Lunch
+Hours</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Time Off
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(PTO, Holiday, Bereavement, etc.)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1654,15 +1679,17 @@
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1687,13 +1714,13 @@
         <v>16</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>14</v>
@@ -1757,35 +1784,39 @@
       <c r="B3" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="C3" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.55208333333333337</v>
+      </c>
       <c r="E3" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>5.5833333333333348</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>16</v>
+        <v>2.7499999999999982</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -1906,7 +1937,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>26.38333333333334</v>
+        <v>25.633333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -1918,7 +1949,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>13.61666666666666</v>
+        <v>14.366666666666667</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A61724-6549-4F88-8E4B-22B34DE23C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF93349-117A-4E1F-A7A5-27CC03CD372D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -1693,7 +1693,7 @@
     <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
         <v>03/09/2026</v>
@@ -1791,7 +1791,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="E3" s="9">
-        <v>0.66666666666666663</v>
+        <v>0.66736111111111107</v>
       </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
@@ -1804,11 +1804,11 @@
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>2.7499999999999982</v>
+        <v>2.7666666666666648</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3333333333333321</v>
+        <v>8.35</v>
       </c>
       <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -1824,26 +1824,30 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Wed (11th)</v>
       </c>
-      <c r="B4" s="8"/>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K4" s="13" t="str">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
@@ -1937,7 +1941,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>25.633333333333333</v>
+        <v>34.733333333333341</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -1949,7 +1953,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>14.366666666666667</v>
+        <v>5.2666666666666586</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF93349-117A-4E1F-A7A5-27CC03CD372D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802804B5-89BF-4E0C-9456-488797C07938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="4185" yWindow="1920" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260309" sheetId="10" r:id="rId1"/>
@@ -1827,35 +1827,39 @@
       <c r="B4" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="C4" s="8">
+        <v>0.54027777777777775</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5708333333333333</v>
+      </c>
       <c r="E4" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>6.05</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>16</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -1864,7 +1868,7 @@
         <v>Thu (12th)</v>
       </c>
       <c r="B5" s="8">
-        <v>0.28819444444444442</v>
+        <v>0.28888888888888886</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1880,7 +1884,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>-6.9166666666666661</v>
+        <v>-6.9333333333333327</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
@@ -1888,7 +1892,7 @@
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>9.0833333333333339</v>
+        <v>9.0666666666666664</v>
       </c>
       <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
@@ -1941,7 +1945,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>34.733333333333341</v>
+        <v>33.983333333333334</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -1953,7 +1957,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>5.2666666666666586</v>
+        <v>6.0166666666666657</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802804B5-89BF-4E0C-9456-488797C07938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA68902D-4EC8-4CEA-8EE8-0B59C5B45D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4185" yWindow="1920" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="4050" yWindow="1710" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260309" sheetId="10" r:id="rId1"/>
@@ -1870,37 +1870,41 @@
       <c r="B5" s="8">
         <v>0.28888888888888886</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="C5" s="8">
+        <v>0.49791666666666667</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52916666666666667</v>
+      </c>
       <c r="E5" s="9">
         <v>0.625</v>
       </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" s="28">
         <v>1</v>
       </c>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>-6.9333333333333327</v>
+        <v>5.0166666666666675</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>9.0666666666666664</v>
-      </c>
-      <c r="K5" s="13" t="str">
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L5" s="14">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>-19.999999999999986</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -1945,7 +1949,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>33.983333333333334</v>
+        <v>33.233333333333334</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -1957,7 +1961,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>6.0166666666666657</v>
+        <v>6.7666666666666657</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA68902D-4EC8-4CEA-8EE8-0B59C5B45D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFC1A54-34DB-4091-BA74-75525E4CB85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4050" yWindow="1710" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="41595" yWindow="1845" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260309" sheetId="10" r:id="rId1"/>
@@ -1912,26 +1912,30 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Fri (13th)</v>
       </c>
-      <c r="B6" s="8"/>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K6" s="13" t="str">
         <f t="shared" si="4"/>
@@ -1949,7 +1953,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>33.233333333333334</v>
+        <v>42.31666666666667</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -1961,7 +1965,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>6.7666666666666657</v>
+        <v>-2.31666666666667</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -1969,9 +1973,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25" t="str">
+      <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>-</v>
+        <v>2.31666666666667</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFC1A54-34DB-4091-BA74-75525E4CB85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7518B91C-73EB-4E96-B4F7-5A1327CB3BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41595" yWindow="1845" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="4860" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260309" sheetId="10" r:id="rId1"/>
@@ -1915,35 +1915,39 @@
       <c r="B6" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="8">
+        <v>0.50208333333333333</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53263888888888888</v>
+      </c>
       <c r="E6" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>5.1333333333333337</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>3.2166666666666659</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K6" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
         <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
@@ -1953,7 +1957,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>42.31666666666667</v>
+        <v>41.583333333333336</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -1965,7 +1969,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>-2.31666666666667</v>
+        <v>-1.5833333333333357</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -1975,7 +1979,7 @@
       </c>
       <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>2.31666666666667</v>
+        <v>1.5833333333333357</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7518B91C-73EB-4E96-B4F7-5A1327CB3BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30B14B8-A433-40B1-B840-57A2EEB581B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4860" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260309" sheetId="10" r:id="rId1"/>
-    <sheet name="20260302" sheetId="9" r:id="rId2"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId3"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId4"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId5"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId6"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId7"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId8"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId9"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId10"/>
+    <sheet name="20260316" sheetId="11" r:id="rId1"/>
+    <sheet name="20260309" sheetId="10" r:id="rId2"/>
+    <sheet name="20260302" sheetId="9" r:id="rId3"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId4"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId5"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId7"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId8"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId9"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId10"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -609,7 +610,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="82">
+  <dxfs count="91">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -855,6 +856,93 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1675,6 +1763,1065 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>03/16/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (16th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.53263888888888888</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.1166666666666671</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.2166666666666659</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (17th)</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="str">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (18th)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (19th)</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (20th)</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>8.3333333333333321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>31.666666666666668</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25" t="str">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/12/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (12th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9000000000000012</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.35</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (13th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.366666666666668</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.9833333333333316</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.35</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (14th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.4333333333333327</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (15th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0666666666666664</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-14.99999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (16th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.4499999999999993</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.916666666666667</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.6499999999999986</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4333333333333318</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.2833333333333332</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>3.466666666666665</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44.000000000000085</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6166666666666654</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.7999999999999972</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2067,357 +3214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49375000000000002</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4333333333333318</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57152777777777775</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.2833333333333332</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52222222222222225</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>3.466666666666665</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44.000000000000085</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3999999999999986</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.6166666666666654</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.7999999999999972</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2806,7 +3603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3182,7 +3979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3564,7 +4361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3946,7 +4743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4326,7 +5123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4676,7 +5473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5024,354 +5821,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/12/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (12th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49236111111111114</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9000000000000012</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4499999999999984</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.35</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (13th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.58402777777777781</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.366666666666668</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.9833333333333316</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.35</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (14th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56527777777777777</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.916666666666667</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.4333333333333327</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (15th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50555555555555554</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53611111111111109</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66805555555555551</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>5.0666666666666664</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.2333333333333325</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-14.99999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (16th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.51527777777777772</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.4499999999999993</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.916666666666667</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.6499999999999986</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30B14B8-A433-40B1-B840-57A2EEB581B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CC6B32-722C-4093-B51A-A3C4CAAC8567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4860" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -1869,34 +1869,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Tue (17th)</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53263888888888888</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>0</v>
+        <v>5.1000000000000005</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>0</v>
+        <v>3.2166666666666659</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>46</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-19.999999999999986</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -2011,7 +2019,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>8.3333333333333321</v>
+        <v>16.649999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2023,7 +2031,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>31.666666666666668</v>
+        <v>23.35</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CC6B32-722C-4093-B51A-A3C4CAAC8567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A132932-E5DB-42CD-B64A-5CDBEA23EA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4860" yWindow="1575" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="4155" yWindow="1095" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260316" sheetId="11" r:id="rId1"/>
@@ -1912,34 +1912,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Wed (18th)</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.61041666666666672</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>7.0000000000000018</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>1.3499999999999979</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -1947,34 +1955,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (19th)</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L5" s="14">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -2019,7 +2035,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>16.649999999999999</v>
+        <v>33.333333333333329</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2031,7 +2047,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>23.35</v>
+        <v>6.6666666666666714</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A132932-E5DB-42CD-B64A-5CDBEA23EA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B18E397-AC1D-42C6-A9D7-0FC3CB42B666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4155" yWindow="1095" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260316" sheetId="11" r:id="rId1"/>
-    <sheet name="20260309" sheetId="10" r:id="rId2"/>
-    <sheet name="20260302" sheetId="9" r:id="rId3"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId4"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId5"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId7"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId8"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId9"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId10"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId11"/>
+    <sheet name="20260323" sheetId="12" r:id="rId1"/>
+    <sheet name="20260316" sheetId="11" r:id="rId2"/>
+    <sheet name="20260309" sheetId="10" r:id="rId3"/>
+    <sheet name="20260302" sheetId="9" r:id="rId4"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId5"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId6"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId7"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId8"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId9"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId10"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId11"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -610,7 +611,94 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="91">
+  <dxfs count="100">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1763,6 +1851,1407 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>03/23/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (23rd)</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="13" t="str">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (24th)</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="str">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (25th)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (26th)</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (27th)</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>40</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25" t="str">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/19/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (19th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55069444444444449</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.7833333333333314</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (20th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>4.5333333333333332</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.666666666666667</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.999999999999922</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-12.999999999999957</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (21st)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.2902777777777778</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56736111111111109</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.9499999999999993</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.3833333333333329</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (22nd)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.59583333333333333</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999993</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (23rd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.29583333333333334</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.56041666666666667</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.35</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>1.8333333333333321</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.1833333333333318</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-11.999999999999908</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.449999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.4499999999999957</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="27" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/12/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (12th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9000000000000012</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.35</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (13th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.366666666666668</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.9833333333333316</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.35</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (14th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.4333333333333327</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (15th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0666666666666664</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-14.99999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (16th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.4499999999999993</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.916666666666667</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.6499999999999986</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="20" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4333333333333318</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.2833333333333332</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>3.466666666666665</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44.000000000000085</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6166666666666654</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.7999999999999972</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -1998,34 +3487,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Fri (20th)</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K6" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L6" s="14">
         <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
@@ -2035,7 +3532,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>33.333333333333329</v>
+        <v>41.666666666666657</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2047,7 +3544,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>6.6666666666666714</v>
+        <v>-1.6666666666666572</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2055,9 +3552,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25" t="str">
+      <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>-</v>
+        <v>1.6666666666666572</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -2106,37 +3603,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="97" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="96" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="95" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="94" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2145,707 +3642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/12/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (12th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49236111111111114</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9000000000000012</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4499999999999984</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.35</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (13th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.58402777777777781</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.366666666666668</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.9833333333333316</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.35</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (14th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56527777777777777</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.916666666666667</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.4333333333333327</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (15th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50555555555555554</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53611111111111109</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66805555555555551</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>5.0666666666666664</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.2333333333333325</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-14.99999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (16th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.51527777777777772</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.4499999999999993</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.916666666666667</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.6499999999999986</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49375000000000002</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4333333333333318</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57152777777777775</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.2833333333333332</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52222222222222225</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>3.466666666666665</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44.000000000000085</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3999999999999986</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.6166666666666654</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.7999999999999972</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3199,37 +3996,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3238,7 +4035,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3588,37 +4385,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3627,7 +4424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3964,37 +4761,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4003,7 +4800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4346,37 +5143,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4385,7 +5182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4728,37 +5525,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4767,7 +5564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5108,37 +5905,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5147,7 +5944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5466,379 +6263,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/19/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (19th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55069444444444449</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.7833333333333314</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (20th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.48333333333333334</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.51388888888888884</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>4.5333333333333332</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.666666666666667</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.999999999999922</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-12.999999999999957</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (21st)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.2902777777777778</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56736111111111109</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.9499999999999993</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.3833333333333329</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>42.000000000000014</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (22nd)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.56597222222222221</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.59583333333333333</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>6.666666666666667</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>1.6999999999999993</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (23rd)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.29583333333333334</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.56041666666666667</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.59027777777777779</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>6.35</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>1.8333333333333321</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.1833333333333318</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-11.999999999999908</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.449999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.4499999999999957</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B18E397-AC1D-42C6-A9D7-0FC3CB42B666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF27A0FC-98BF-4588-8C33-4788083D6858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4155" yWindow="1095" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -681,6 +681,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -690,6 +700,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -701,6 +718,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -711,6 +748,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -897,53 +944,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1913,26 +1913,30 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Mon (23rd)</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K2" s="13" t="str">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
@@ -2091,7 +2095,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>40</v>
+        <v>30.916666666666664</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2162,37 +2166,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="97" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="96" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="95" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="94" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2520,29 +2524,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="27" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2870,29 +2874,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="22" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="20" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3220,29 +3224,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3603,37 +3607,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="99" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="97" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="95" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="93" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3996,37 +4000,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4385,37 +4389,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4761,37 +4765,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5143,37 +5147,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5525,37 +5529,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5905,37 +5909,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6263,29 +6267,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="36" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF27A0FC-98BF-4588-8C33-4788083D6858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24475083-C926-41B2-AB28-B2863E6045E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="1095" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="6525" yWindow="1920" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260323" sheetId="12" r:id="rId1"/>
@@ -1916,35 +1916,39 @@
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="8">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.56736111111111109</v>
+      </c>
       <c r="E2" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>5.95</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>16</v>
+        <v>2.3833333333333329</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K2" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
       <c r="M2" s="15"/>
     </row>
@@ -2095,7 +2099,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>9.0833333333333339</v>
+        <v>8.3333333333333321</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2107,7 +2111,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>30.916666666666664</v>
+        <v>31.666666666666668</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24475083-C926-41B2-AB28-B2863E6045E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A6408F-1B88-44B0-BEF5-AA9E1C9B8FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6525" yWindow="1920" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -1957,34 +1957,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Tue (24th)</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53055555555555556</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>0</v>
+        <v>5.0833333333333339</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>0</v>
+        <v>3.2666666666666657</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -2099,7 +2107,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>8.3333333333333321</v>
+        <v>16.68333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2111,7 +2119,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>31.666666666666668</v>
+        <v>23.31666666666667</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A6408F-1B88-44B0-BEF5-AA9E1C9B8FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5BDD23-6F50-49D8-909A-DF1E7EBE75E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6525" yWindow="1920" windowWidth="24360" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="4380" yWindow="1725" windowWidth="26235" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260323" sheetId="12" r:id="rId1"/>
@@ -2000,34 +2000,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Wed (25th)</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>5.3666666666666663</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>2.9833333333333334</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -2035,34 +2043,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (26th)</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.3833333333333329</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.9833333333333334</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="13" t="str">
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>-23.000000000000028</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -2107,7 +2123,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>16.68333333333333</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2119,7 +2135,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>23.31666666666667</v>
+        <v>6.6000000000000014</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5BDD23-6F50-49D8-909A-DF1E7EBE75E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68A70FC-5277-4F43-85CD-AD48383EBBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="1725" windowWidth="26235" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="3015" yWindow="3120" windowWidth="27180" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260323" sheetId="12" r:id="rId1"/>
-    <sheet name="20260316" sheetId="11" r:id="rId2"/>
-    <sheet name="20260309" sheetId="10" r:id="rId3"/>
-    <sheet name="20260302" sheetId="9" r:id="rId4"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId5"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId6"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId7"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId8"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId9"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId10"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId11"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId12"/>
+    <sheet name="20260330" sheetId="13" r:id="rId1"/>
+    <sheet name="20260323" sheetId="12" r:id="rId2"/>
+    <sheet name="20260316" sheetId="11" r:id="rId3"/>
+    <sheet name="20260309" sheetId="10" r:id="rId4"/>
+    <sheet name="20260302" sheetId="9" r:id="rId5"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId6"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId8"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId9"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId10"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId11"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId12"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -520,7 +521,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -606,12 +607,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="100">
+  <dxfs count="113">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1513,6 +1515,133 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1851,6 +1980,1769 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>03/30/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (30th)</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="13" t="str">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (31st)</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="str">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (1st)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (2nd)</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (3rd)</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>40</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25" t="str">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/26/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (26th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.29236111111111113</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.47847222222222224</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.4666666666666668</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.8</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>42.999999999999929</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-16.999999999999943</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (27th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57847222222222228</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.2500000000000018</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.1166666666666645</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (28th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.58263888888888893</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>6.3333333333333348</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.0166666666666648</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (29th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.1833333333333336</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (30th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.6333333333333346</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.716666666666665</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.683333333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.6833333333333371</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/19/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (19th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55069444444444449</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.7833333333333314</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (20th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>4.5333333333333332</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.666666666666667</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.999999999999922</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-12.999999999999957</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (21st)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.2902777777777778</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56736111111111109</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.9499999999999993</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.3833333333333329</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (22nd)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.59583333333333333</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999993</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (23rd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.29583333333333334</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.56041666666666667</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.35</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>1.8333333333333321</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.1833333333333318</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-11.999999999999908</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.449999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.4499999999999957</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/12/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (12th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9000000000000012</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.35</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (13th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.366666666666668</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.9833333333333316</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.35</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (14th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.4333333333333327</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (15th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0666666666666664</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-14.99999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (16th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.4499999999999993</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.916666666666667</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.6499999999999986</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4333333333333318</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.2833333333333332</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>3.466666666666665</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44.000000000000085</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6166666666666654</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.7999999999999972</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2086,34 +3978,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Fri (27th)</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>0</v>
+        <v>5.5666666666666682</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.7499999999999982</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="13" t="str">
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K6" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
+        <v>46</v>
+      </c>
+      <c r="L6" s="14">
         <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-19.999999999999986</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
@@ -2123,7 +4023,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>33.4</v>
+        <v>41.716666666666669</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.3</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2135,7 +4039,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>6.6000000000000014</v>
+        <v>-1.7166666666666686</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2143,9 +4047,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25" t="str">
+      <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>-</v>
+        <v>1.7166666666666686</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -2194,37 +4098,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="99" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="100" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="97" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="95" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="97" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="96" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="2" operator="lessThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="93" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2233,1057 +4145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/19/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (19th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55069444444444449</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.7833333333333314</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (20th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.48333333333333334</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.51388888888888884</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>4.5333333333333332</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.666666666666667</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.999999999999922</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-12.999999999999957</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (21st)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.2902777777777778</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56736111111111109</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.9499999999999993</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.3833333333333329</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>42.000000000000014</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (22nd)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.56597222222222221</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.59583333333333333</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>6.666666666666667</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>1.6999999999999993</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (23rd)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.29583333333333334</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.56041666666666667</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.59027777777777779</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>6.35</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>1.8333333333333321</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.1833333333333318</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-11.999999999999908</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.449999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.4499999999999957</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/12/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (12th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49236111111111114</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9000000000000012</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4499999999999984</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.35</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (13th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.58402777777777781</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.366666666666668</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.9833333333333316</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.35</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (14th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56527777777777777</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.916666666666667</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.4333333333333327</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (15th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50555555555555554</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53611111111111109</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66805555555555551</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>5.0666666666666664</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.2333333333333325</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-14.99999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (16th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.51527777777777772</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.4499999999999993</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.916666666666667</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.6499999999999986</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49375000000000002</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4333333333333318</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57152777777777775</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.2833333333333332</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52222222222222225</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>3.466666666666665</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44.000000000000085</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3999999999999986</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.6166666666666654</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.7999999999999972</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3566,6 +4428,10 @@
         <f>SUM(J2:J6)</f>
         <v>41.666666666666657</v>
       </c>
+      <c r="K7" s="33">
+        <f>((60*5) - SUM(K2:K6)) / 60</f>
+        <v>1.25</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -3674,7 +4540,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3959,6 +4825,10 @@
         <f>SUM(J2:J6)</f>
         <v>41.583333333333336</v>
       </c>
+      <c r="K7" s="33">
+        <f>((60*5) - SUM(K2:K6)) / 60</f>
+        <v>1.1666666666666685</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -4067,7 +4937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4348,6 +5218,10 @@
         <f>SUM(J2:J6)</f>
         <v>41.93333333333333</v>
       </c>
+      <c r="K7" s="33">
+        <f>((60*5) - SUM(K2:K6)) / 60</f>
+        <v>1.4833333333333338</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -4456,7 +5330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4832,7 +5706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5214,7 +6088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5596,7 +6470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5974,354 +6848,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/26/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (26th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.29236111111111113</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.47847222222222224</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5083333333333333</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.4666666666666668</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.8</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.2666666666666657</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>42.999999999999929</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-16.999999999999943</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (27th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57847222222222228</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.2500000000000018</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.1166666666666645</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (28th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.58263888888888893</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>6.3333333333333348</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.0166666666666648</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (29th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50416666666666665</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>5.1833333333333336</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (30th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28888888888888886</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.6333333333333346</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.716666666666665</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.683333333333337</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.6833333333333371</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68A70FC-5277-4F43-85CD-AD48383EBBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C71BCA-CDEF-4CAA-8410-A2CDD3B4FE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3015" yWindow="3120" windowWidth="27180" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="3615" yWindow="2010" windowWidth="27180" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260330" sheetId="13" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2042,34 +2042,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Mon (30th)</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.48541666666666666</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.51666666666666672</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>0</v>
+        <v>4.7333333333333343</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>0</v>
+        <v>3.5999999999999979</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
+        <v>45.000000000000078</v>
+      </c>
+      <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
       <c r="M2" s="15"/>
     </row>
@@ -2220,11 +2228,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>0</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>0</v>
+        <v>4.2499999999999982</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2236,7 +2244,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>40</v>
+        <v>31.666666666666668</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C71BCA-CDEF-4CAA-8410-A2CDD3B4FE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3753568F-7E8E-4B06-B394-4BB317B426CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3615" yWindow="2010" windowWidth="27180" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -2086,34 +2086,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Tue (31st)</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53680555555555554</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>0</v>
+        <v>5.2166666666666668</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>0</v>
+        <v>3.1166666666666663</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -2121,34 +2129,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Wed (1st)</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.57708333333333328</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>6.1999999999999993</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>2.1500000000000004</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -2228,11 +2244,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>8.3333333333333321</v>
+        <v>25.016666666666666</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>4.2499999999999982</v>
+        <v>2.7666666666666653</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2244,7 +2260,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>31.666666666666668</v>
+        <v>14.983333333333334</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3753568F-7E8E-4B06-B394-4BB317B426CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C6B4EF-1D8E-4AAD-8FFE-16CFF0FE765F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3615" yWindow="2010" windowWidth="27180" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -2139,7 +2139,7 @@
         <v>0.57708333333333328</v>
       </c>
       <c r="E4" s="9">
-        <v>0.66666666666666663</v>
+        <v>0.66736111111111107</v>
       </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
@@ -2152,11 +2152,11 @@
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.1500000000000004</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>8.35</v>
+        <v>8.3666666666666671</v>
       </c>
       <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
+        <v>-23.000000000000028</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -2172,34 +2172,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (2nd)</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50902777777777775</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.5395833333333333</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -2207,34 +2215,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Fri (3rd)</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.49583333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>0</v>
+        <v>4.9833333333333343</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.3499999999999988</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K6" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L6" s="14">
         <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
@@ -2244,11 +2260,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>25.016666666666666</v>
+        <v>41.716666666666669</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.7666666666666653</v>
+        <v>1.2833333333333319</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2260,7 +2276,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>14.983333333333334</v>
+        <v>-1.7166666666666686</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2268,9 +2284,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25" t="str">
+      <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>-</v>
+        <v>1.7166666666666686</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C6B4EF-1D8E-4AAD-8FFE-16CFF0FE765F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B54FF9-C5DE-4D3E-8973-0457ADA34CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3615" yWindow="2010" windowWidth="27180" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260330" sheetId="13" r:id="rId1"/>
-    <sheet name="20260323" sheetId="12" r:id="rId2"/>
-    <sheet name="20260316" sheetId="11" r:id="rId3"/>
-    <sheet name="20260309" sheetId="10" r:id="rId4"/>
-    <sheet name="20260302" sheetId="9" r:id="rId5"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId6"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId8"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId9"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId10"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId11"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId12"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId13"/>
+    <sheet name="20260408" sheetId="14" r:id="rId1"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId2"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId3"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId4"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId5"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId6"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId7"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId8"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId9"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId10"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId11"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId12"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId13"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -70,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -613,7 +614,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="113">
+  <dxfs count="124">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1428,6 +1429,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1980,6 +2088,2157 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>04/08/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (8th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9166666666666679</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4166666666666652</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (9th)</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="str">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (10th)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Sat (11th)</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Sun (12th)</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>31.666666666666668</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25" t="str">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="56.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>02/02/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (2nd)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>COUNT(B2:E2)</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>6.2166666666666686</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.166666666666667</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3833333333333364</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>41.999999999999851</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-24.000000000000185</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (3rd)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.29236111111111113</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F5" si="0">COUNT(B3:E3)</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.35</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.9166666666666652</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-16.999999999999943</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (4th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.57777777777777772</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.1999999999999993</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.1333333333333337</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (5th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.8166666666666664</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.549999999999998</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666636</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000085</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-22.999999999999815</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (6th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F6" s="30">
+        <f>COUNT(B6:E6)</f>
+        <v>2</v>
+      </c>
+      <c r="G6" s="11">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-7</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.349999999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.3499999999999943</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/26/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (26th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.29236111111111113</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.47847222222222224</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.4666666666666668</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.8</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>42.999999999999929</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-16.999999999999943</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (27th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57847222222222228</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.2500000000000018</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.1166666666666645</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (28th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.58263888888888893</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>6.3333333333333348</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.0166666666666648</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (29th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.1833333333333336</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (30th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.6333333333333346</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.716666666666665</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.683333333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.6833333333333371</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/19/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (19th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55069444444444449</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.7833333333333314</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (20th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>4.5333333333333332</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.666666666666667</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.999999999999922</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-12.999999999999957</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (21st)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.2902777777777778</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56736111111111109</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.9499999999999993</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.3833333333333329</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (22nd)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.59583333333333333</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999993</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (23rd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.29583333333333334</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.56041666666666667</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.35</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>1.8333333333333321</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.1833333333333318</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-11.999999999999908</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.449999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.4499999999999957</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/12/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (12th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9000000000000012</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.35</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (13th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.366666666666668</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.9833333333333316</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.35</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (14th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.4333333333333327</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (15th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0666666666666664</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-14.99999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (16th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.4499999999999993</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.916666666666667</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.6499999999999986</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4333333333333318</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.2833333333333332</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>3.466666666666665</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44.000000000000085</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6166666666666654</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.7999999999999972</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2382,1407 +4641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/26/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (26th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.29236111111111113</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.47847222222222224</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5083333333333333</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.4666666666666668</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.8</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.2666666666666657</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>42.999999999999929</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-16.999999999999943</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (27th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57847222222222228</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.2500000000000018</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.1166666666666645</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (28th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.58263888888888893</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>6.3333333333333348</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.0166666666666648</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (29th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50416666666666665</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>5.1833333333333336</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (30th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28888888888888886</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.6333333333333346</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.716666666666665</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.683333333333337</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.6833333333333371</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/19/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (19th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55069444444444449</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.7833333333333314</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (20th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.48333333333333334</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.51388888888888884</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>4.5333333333333332</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.666666666666667</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.999999999999922</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-12.999999999999957</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (21st)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.2902777777777778</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56736111111111109</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.9499999999999993</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.3833333333333329</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>42.000000000000014</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (22nd)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.56597222222222221</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.59583333333333333</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>6.666666666666667</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>1.6999999999999993</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (23rd)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.29583333333333334</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.56041666666666667</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.59027777777777779</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>6.35</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>1.8333333333333321</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.1833333333333318</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-11.999999999999908</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.449999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.4499999999999957</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/12/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (12th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49236111111111114</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9000000000000012</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4499999999999984</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.35</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (13th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.58402777777777781</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.366666666666668</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.9833333333333316</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.35</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (14th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56527777777777777</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.916666666666667</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.4333333333333327</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (15th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50555555555555554</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53611111111111109</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66805555555555551</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>5.0666666666666664</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.2333333333333325</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-14.99999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (16th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.51527777777777772</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.4499999999999993</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.916666666666667</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.6499999999999986</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49375000000000002</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4333333333333318</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57152777777777775</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.2833333333333332</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52222222222222225</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>3.466666666666665</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44.000000000000085</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3999999999999986</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.6166666666666654</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.7999999999999972</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4185,7 +5044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4580,7 +5439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4977,7 +5836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5370,7 +6229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5746,7 +6605,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6128,7 +6987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6508,384 +7367,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="56.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>02/02/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (2nd)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.54722222222222228</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.57638888888888884</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>COUNT(B2:E2)</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>6.2166666666666686</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.166666666666667</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3833333333333364</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>41.999999999999851</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-24.000000000000185</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (3rd)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.29236111111111113</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.55694444444444446</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.58680555555555558</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F5" si="0">COUNT(B3:E3)</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.35</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.9166666666666652</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.2666666666666657</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-16.999999999999943</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (4th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54652777777777772</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.57777777777777772</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.1999999999999993</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.1333333333333337</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (5th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.48888888888888887</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.51875000000000004</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>4.8166666666666664</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.549999999999998</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666636</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000085</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-22.999999999999815</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (6th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F6" s="30">
-        <f>COUNT(B6:E6)</f>
-        <v>2</v>
-      </c>
-      <c r="G6" s="11">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>-7</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.349999999999994</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.3499999999999943</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B54FF9-C5DE-4D3E-8973-0457ADA34CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A944511F-090B-4506-9335-BEB061EDD74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3615" yWindow="2010" windowWidth="27180" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -2194,34 +2194,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (9th)</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>0</v>
+        <v>4.9500000000000011</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>0</v>
+        <v>3.3999999999999986</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -2336,11 +2344,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>8.3333333333333321</v>
+        <v>16.68333333333333</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>4.25</v>
+        <v>3.5166666666666666</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2352,7 +2360,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>31.666666666666668</v>
+        <v>23.31666666666667</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A944511F-090B-4506-9335-BEB061EDD74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA384AAD-4773-4613-9510-E91B7AEDDE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="2010" windowWidth="27180" windowHeight="16905" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="2565" yWindow="960" windowWidth="21555" windowHeight="19800" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260408" sheetId="14" r:id="rId1"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId2"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId3"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId4"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId5"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId6"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId7"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId8"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId9"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId10"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId11"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId12"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId13"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId14"/>
+    <sheet name="20260413" sheetId="15" r:id="rId1"/>
+    <sheet name="20260408" sheetId="14" r:id="rId2"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId3"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId4"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId5"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId6"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId7"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId9"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId10"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId11"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId12"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId13"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId14"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -71,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -614,7 +615,114 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="124">
+  <dxfs count="135">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2088,6 +2196,2531 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>04/13/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (13th)</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="13" t="str">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (14th)</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="str">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (15th)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (16th)</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (17th)</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>40</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25" t="str">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="56.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>02/09/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (9th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49861111111111112</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>COUNT(B2:E2)</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.0500000000000007</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.2999999999999989</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (10th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.49861111111111112</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">COUNT(B3:E3)</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.0500000000000007</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.2999999999999989</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (11th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56388888888888888</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.8666666666666671</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.4666666666666659</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (12th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53125</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.1333333333333337</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.2499999999999991</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.999999999999972</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (13th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.47986111111111113</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>4.6000000000000014</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.75</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3500000000000014</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>43.999999999999922</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-22.000000000000085</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.766666666666666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.7666666666666657</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="56" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="52" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="56.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>02/02/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (2nd)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>COUNT(B2:E2)</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>6.2166666666666686</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.166666666666667</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3833333333333364</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>41.999999999999851</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-24.000000000000185</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (3rd)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.29236111111111113</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F5" si="0">COUNT(B3:E3)</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.35</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.9166666666666652</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-16.999999999999943</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (4th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.57777777777777772</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.1999999999999993</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.1333333333333337</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (5th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.8166666666666664</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.549999999999998</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666636</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000085</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-22.999999999999815</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (6th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F6" s="30">
+        <f>COUNT(B6:E6)</f>
+        <v>2</v>
+      </c>
+      <c r="G6" s="11">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-7</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.349999999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.3499999999999943</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="45" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="43" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/26/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (26th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.29236111111111113</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.47847222222222224</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.4666666666666668</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.8</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>42.999999999999929</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-16.999999999999943</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (27th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57847222222222228</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.2500000000000018</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.1166666666666645</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (28th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.58263888888888893</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>6.3333333333333348</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.0166666666666648</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (29th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.1833333333333336</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (30th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.6333333333333346</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.716666666666665</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.683333333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.6833333333333371</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="36" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/19/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (19th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55069444444444449</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.7833333333333314</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (20th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>4.5333333333333332</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.666666666666667</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.999999999999922</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-12.999999999999957</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (21st)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.2902777777777778</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56736111111111109</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.9499999999999993</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.3833333333333329</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (22nd)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.59583333333333333</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999993</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (23rd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.29583333333333334</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.56041666666666667</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.35</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>1.8333333333333321</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.1833333333333318</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-11.999999999999908</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.449999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.4499999999999957</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="31" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="29" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/12/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (12th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9000000000000012</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.35</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (13th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.366666666666668</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.9833333333333316</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.35</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (14th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.4333333333333327</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (15th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0666666666666664</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-14.99999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (16th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.4499999999999993</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.916666666666667</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.6499999999999986</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4333333333333318</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.2833333333333332</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>3.466666666666665</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44.000000000000085</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6166666666666654</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.7999999999999972</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2237,34 +4870,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Fri (10th)</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49027777777777776</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>3.4499999999999984</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.2999999999999972</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>47.000000000000071</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-18.999999999999829</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -2272,34 +4913,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Sat (11th)</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.8833333333333329</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.4499999999999984</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>45.000000000000078</v>
+      </c>
+      <c r="L5" s="14">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -2307,34 +4956,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Sun (12th)</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.49861111111111112</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>0</v>
+        <v>5.0500000000000007</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.2999999999999989</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
         <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
@@ -2344,11 +5001,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>16.68333333333333</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>3.5166666666666666</v>
+        <v>1.2499999999999976</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2360,7 +5017,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>23.31666666666667</v>
+        <v>-1.6666666666666643</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2368,9 +5025,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25" t="str">
+      <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>-</v>
+        <v>1.6666666666666643</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -2419,45 +5076,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2466,1787 +5123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="56.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>02/02/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (2nd)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.54722222222222228</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.57638888888888884</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>COUNT(B2:E2)</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>6.2166666666666686</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.166666666666667</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3833333333333364</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>41.999999999999851</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-24.000000000000185</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (3rd)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.29236111111111113</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.55694444444444446</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.58680555555555558</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F5" si="0">COUNT(B3:E3)</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.35</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.9166666666666652</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.2666666666666657</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-16.999999999999943</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (4th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54652777777777772</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.57777777777777772</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.1999999999999993</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.1333333333333337</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (5th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.48888888888888887</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.51875000000000004</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>4.8166666666666664</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.549999999999998</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666636</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000085</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-22.999999999999815</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (6th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F6" s="30">
-        <f>COUNT(B6:E6)</f>
-        <v>2</v>
-      </c>
-      <c r="G6" s="11">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>-7</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.349999999999994</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.3499999999999943</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/26/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (26th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.29236111111111113</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.47847222222222224</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5083333333333333</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.4666666666666668</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.8</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.2666666666666657</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>42.999999999999929</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-16.999999999999943</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (27th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57847222222222228</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.2500000000000018</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.1166666666666645</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (28th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.58263888888888893</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>6.3333333333333348</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.0166666666666648</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (29th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50416666666666665</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>5.1833333333333336</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (30th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28888888888888886</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.6333333333333346</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.716666666666665</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.683333333333337</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.6833333333333371</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/19/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (19th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55069444444444449</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.7833333333333314</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (20th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.48333333333333334</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.51388888888888884</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>4.5333333333333332</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.666666666666667</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.999999999999922</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-12.999999999999957</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (21st)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.2902777777777778</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56736111111111109</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.9499999999999993</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.3833333333333329</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>42.000000000000014</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (22nd)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.56597222222222221</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.59583333333333333</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>6.666666666666667</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>1.6999999999999993</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (23rd)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.29583333333333334</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.56041666666666667</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.59027777777777779</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>6.35</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>1.8333333333333321</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.1833333333333318</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-11.999999999999908</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.449999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.4499999999999957</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/12/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (12th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49236111111111114</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9000000000000012</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4499999999999984</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.35</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (13th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.58402777777777781</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.366666666666668</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.9833333333333316</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.35</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (14th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56527777777777777</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.916666666666667</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.4333333333333327</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (15th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50555555555555554</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53611111111111109</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66805555555555551</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>5.0666666666666664</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.2333333333333325</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-14.99999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (16th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.51527777777777772</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.4499999999999993</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.916666666666667</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.6499999999999986</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49375000000000002</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4333333333333318</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57152777777777775</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.2833333333333332</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52222222222222225</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>3.466666666666665</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44.000000000000085</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3999999999999986</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.6166666666666654</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.7999999999999972</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4602,45 +5479,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4649,7 +5526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5005,45 +5882,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="101" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="99" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="97" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="93" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5052,7 +5929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5408,37 +6285,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="100" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="97" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="96" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="94" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="93" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5447,7 +6324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5805,37 +6682,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="88" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="87" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="84" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5844,7 +6721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6198,37 +7075,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="79" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="78" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="75" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6237,7 +7114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6574,37 +7451,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="66" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6613,7 +7490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6956,419 +7833,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="56.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>02/09/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (9th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49861111111111112</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>COUNT(B2:E2)</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.0500000000000007</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.2999999999999989</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.35</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (10th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.49861111111111112</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">COUNT(B3:E3)</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.0500000000000007</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.2999999999999989</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.35</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (11th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28888888888888886</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56388888888888888</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.8666666666666671</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.4666666666666659</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (12th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50138888888888888</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53125</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.1333333333333337</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.2499999999999991</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-23.999999999999972</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (13th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.47986111111111113</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>4.6000000000000014</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3.75</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3500000000000014</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>43.999999999999922</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-22.000000000000085</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.766666666666666</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.7666666666666657</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="57" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA384AAD-4773-4613-9510-E91B7AEDDE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09D613B-87F8-45E2-806E-C1702324DD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="960" windowWidth="21555" windowHeight="19800" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260413" sheetId="15" r:id="rId1"/>
@@ -645,6 +645,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -655,6 +665,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -684,6 +704,23 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -695,6 +732,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -705,6 +752,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -714,6 +771,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -725,6 +789,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -735,6 +819,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -859,6 +953,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -869,6 +973,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -926,6 +1040,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -936,6 +1060,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -993,6 +1127,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1003,6 +1147,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1368,175 +1522,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2202,8 +2202,7 @@
   <cols>
     <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
@@ -2258,34 +2257,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Mon (13th)</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>0</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>0</v>
+        <v>3.1499999999999995</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="13" t="str">
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
+        <v>46</v>
+      </c>
+      <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-19.999999999999986</v>
       </c>
       <c r="M2" s="15"/>
     </row>
@@ -2294,34 +2301,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Tue (14th)</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.55277777777777781</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>0</v>
+        <v>5.6000000000000014</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>0</v>
+        <v>2.7333333333333316</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -2329,34 +2344,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Wed (15th)</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.4597222222222222</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.49583333333333335</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>4.1166666666666671</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>4.0999999999999988</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.216666666666665</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>52.000000000000057</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-13.999999999999901</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -2436,11 +2459,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>0</v>
+        <v>24.866666666666664</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>0</v>
+        <v>2.6166666666666658</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2452,7 +2475,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>40</v>
+        <v>15.133333333333336</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2511,45 +2534,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2901,37 +2924,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="56" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="52" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3281,37 +3304,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="45" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="43" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3639,29 +3662,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="36" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3989,29 +4012,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="31" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="29" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4339,29 +4362,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4689,29 +4712,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5076,45 +5099,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5479,45 +5502,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5882,45 +5905,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="100" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="97" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="96" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="94" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6285,37 +6308,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="101" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="99" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="97" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="95" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6682,37 +6705,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="92" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="90" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="88" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="86" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7075,37 +7098,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="83" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="81" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="79" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="77" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7451,37 +7474,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="74" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="72" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="70" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="68" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7833,37 +7856,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="63" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09D613B-87F8-45E2-806E-C1702324DD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2AA631-7BE3-4C1D-9D41-37C257101B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260413" sheetId="15" r:id="rId1"/>
@@ -2387,26 +2387,30 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (16th)</v>
       </c>
-      <c r="B5" s="8"/>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
@@ -2459,7 +2463,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>24.866666666666664</v>
+        <v>33.949999999999996</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
@@ -2475,7 +2479,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>15.133333333333336</v>
+        <v>6.0500000000000043</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2AA631-7BE3-4C1D-9D41-37C257101B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FEF434-2FB6-4E37-9CC3-101432852253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="1305" yWindow="1905" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260413" sheetId="15" r:id="rId1"/>
-    <sheet name="20260408" sheetId="14" r:id="rId2"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId3"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId4"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId5"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId6"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId7"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId9"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId10"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId11"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId12"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId13"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId14"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId15"/>
+    <sheet name="20260420" sheetId="16" r:id="rId1"/>
+    <sheet name="20260413" sheetId="15" r:id="rId2"/>
+    <sheet name="20260408" sheetId="14" r:id="rId3"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId4"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId5"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId6"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId7"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId8"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId9"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId10"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId11"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId12"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId13"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId14"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId15"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -615,7 +616,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="135">
+  <dxfs count="146">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1430,6 +1431,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2196,7 +2304,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2216,7 +2324,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>04/13/2026</v>
+        <v>04/20/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2255,16 +2363,16 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (13th)</v>
+        <v>Mon (20th)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C2" s="8">
-        <v>0.50347222222222221</v>
+        <v>0.49583333333333335</v>
       </c>
       <c r="D2" s="8">
-        <v>0.53541666666666665</v>
+        <v>0.52569444444444446</v>
       </c>
       <c r="E2" s="9">
         <v>0.66666666666666663</v>
@@ -2276,141 +2384,121 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>5.166666666666667</v>
+        <v>4.9833333333333343</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>3.1499999999999995</v>
+        <v>3.383333333333332</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>8.3166666666666664</v>
+        <v>8.3666666666666671</v>
       </c>
       <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>46</v>
+        <v>43.000000000000007</v>
       </c>
       <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-19.999999999999986</v>
+        <v>-23.000000000000028</v>
       </c>
       <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (14th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.52152777777777781</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.55277777777777781</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Tue (21st)</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>5.6000000000000014</v>
+        <v>0</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>2.7333333333333316</v>
+        <v>0</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K3" s="13">
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="str">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L3" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
+        <v>-</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (15th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.4597222222222222</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.49583333333333335</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Wed (22nd)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>4.1166666666666671</v>
+        <v>0</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>4.0999999999999988</v>
+        <v>0</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>8.216666666666665</v>
-      </c>
-      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>52.000000000000057</v>
-      </c>
-      <c r="L4" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-13.999999999999901</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (16th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
+        <v>Thu (23rd)</v>
+      </c>
+      <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+      <c r="E5" s="9"/>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>-6.9166666666666661</v>
+        <v>0</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>9.0833333333333339</v>
+        <v>0</v>
       </c>
       <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
@@ -2424,7 +2512,7 @@
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (17th)</v>
+        <v>Fri (24th)</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2463,11 +2551,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>33.949999999999996</v>
+        <v>8.3666666666666671</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.6166666666666658</v>
+        <v>4.2833333333333332</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2479,7 +2567,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>6.0500000000000043</v>
+        <v>31.633333333333333</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2538,45 +2626,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="145" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="144" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="143" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="142" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="141" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="140" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="139" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="138" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="136" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="135" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2586,6 +2674,388 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>02/16/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (16th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.58958333333333335</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>COUNT(B2:E2)</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>6.5000000000000009</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>1.8499999999999988</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (17th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.47708333333333336</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">COUNT(B3:E3)</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>4.533333333333335</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.8166666666666664</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3500000000000014</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.999999999999922</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-22.000000000000085</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (18th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.57222222222222219</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.2666666666666666</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (19th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53055555555555556</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.2666666666666657</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (20th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>2.333333333333333</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.75</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -2967,7 +3437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3347,7 +3817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3697,7 +4167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4047,7 +4517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4397,7 +4867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4748,6 +5218,408 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>04/13/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (13th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.1499999999999995</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>46</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-19.999999999999986</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (14th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.55277777777777781</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.6000000000000014</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.7333333333333316</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (15th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.4597222222222222</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.49583333333333335</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>4.1166666666666671</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.216666666666665</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>52.000000000000057</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-13.999999999999901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (16th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49930555555555556</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.0666666666666673</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.2999999999999989</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (17th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.51736111111111116</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.5000000000000018</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>2.8666666666666645</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.6</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.1833333333333325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.6000000000000014</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.6000000000000014</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5150,7 +6022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5553,7 +6425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5956,7 +6828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6351,7 +7223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6748,7 +7620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7141,7 +8013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7515,386 +8387,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>02/16/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (16th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.55902777777777779</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.58958333333333335</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>COUNT(B2:E2)</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>6.5000000000000009</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>1.8499999999999988</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.35</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (17th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.47708333333333336</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.50763888888888886</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">COUNT(B3:E3)</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>4.533333333333335</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.8166666666666664</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3500000000000014</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.999999999999922</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-22.000000000000085</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (18th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.57222222222222219</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.2666666666666666</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (19th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53055555555555556</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.1000000000000005</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.2666666666666657</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (20th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.56944444444444442</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>6</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>2.333333333333333</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.75</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,27 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FEF434-2FB6-4E37-9CC3-101432852253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E235E6AF-351E-40B5-9C14-19EFDEEE7331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="1905" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="1245" yWindow="570" windowWidth="28800" windowHeight="16680" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260420" sheetId="16" r:id="rId1"/>
-    <sheet name="20260413" sheetId="15" r:id="rId2"/>
-    <sheet name="20260408" sheetId="14" r:id="rId3"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId4"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId5"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId6"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId7"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId8"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId9"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId10"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId11"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId12"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId13"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId14"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId15"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId16"/>
+    <sheet name="20260427" sheetId="17" r:id="rId1"/>
+    <sheet name="20260420" sheetId="16" r:id="rId2"/>
+    <sheet name="20260413" sheetId="15" r:id="rId3"/>
+    <sheet name="20260408" sheetId="14" r:id="rId4"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId5"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId6"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId7"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId8"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId10"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId11"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId12"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId13"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId14"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId15"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId16"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -616,7 +617,114 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="146">
+  <dxfs count="157">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2304,7 +2412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2324,7 +2432,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>04/20/2026</v>
+        <v>04/27/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2363,51 +2471,43 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (20th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49583333333333335</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52569444444444446</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Mon (27th)</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>4.9833333333333343</v>
+        <v>0</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>3.383333333333332</v>
+        <v>0</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K2" s="13">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13" t="str">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L2" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
+        <v>-</v>
       </c>
       <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (21st)</v>
+        <v>Tue (28th)</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2442,7 +2542,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (22nd)</v>
+        <v>Wed (29th)</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2477,7 +2577,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (23rd)</v>
+        <v>Thu (30th)</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2512,7 +2612,7 @@
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (24th)</v>
+        <v>Fri (1st)</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2551,11 +2651,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>8.3666666666666671</v>
+        <v>0</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>4.2833333333333332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2567,7 +2667,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>31.633333333333333</v>
+        <v>40</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2626,45 +2726,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="145" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="143" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="141" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="139" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="137" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2674,6 +2774,382 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>02/23/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (23rd)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55277777777777781</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="F2" s="30">
+        <f>COUNT(B2:E2)</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.616666666666668</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>1.7333333333333325</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>7.3500000000000005</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>39.999999999999972</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (24th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53125</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F5" si="0">COUNT(B3:E3)</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.2499999999999991</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (25th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.1</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.25</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (26th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.55069444444444449</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.5666666666666682</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>2.7833333333333314</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (27th)</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="30">
+        <f>IF(G6 = 8, 4, IF(G6 = 4, 2, COUNT(B6:E6)))</f>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>8</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-0.39999999999999858</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="74" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="72" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="70" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="68" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3016,37 +3492,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="57" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3055,7 +3531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3398,37 +3874,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="51" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3437,7 +3913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3778,37 +4254,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3817,7 +4293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4136,29 +4612,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4167,7 +4643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4486,29 +4962,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4517,7 +4993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4836,29 +5312,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4867,7 +5343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5186,29 +5662,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5218,6 +5694,408 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>04/20/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (20th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49583333333333335</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52569444444444446</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9833333333333343</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.383333333333332</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (21st)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.48402777777777778</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.51458333333333328</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>4.7000000000000011</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.6500000000000004</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3500000000000014</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.999999999999922</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-22.000000000000085</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (22nd)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49513888888888891</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52569444444444446</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>4.9666666666666677</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>3.383333333333332</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (23rd)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53194444444444444</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.2333333333333325</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (24th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.1833333333333336</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.750000000000007</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.3333333333333344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.7500000000000071</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.7500000000000071</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="156" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="155" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="154" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="152" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="151" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="150" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="149" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="148" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="147" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="146" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5572,45 +6450,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="145" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="144" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="143" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="142" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="141" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="140" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="139" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="138" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="136" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="135" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5619,7 +6497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5975,45 +6853,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6022,7 +6900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6378,45 +7256,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6425,7 +7303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6781,45 +7659,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="101" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="99" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="97" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="93" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6828,7 +7706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7184,37 +8062,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="100" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="97" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="96" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="94" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="93" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7223,7 +8101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7581,37 +8459,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="88" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="87" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="84" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7620,7 +8498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7974,413 +8852,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="79" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="78" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>02/23/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (23rd)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52222222222222225</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55277777777777781</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="F2" s="30">
-        <f>COUNT(B2:E2)</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.616666666666668</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>1.7333333333333325</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>7.3500000000000005</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>39.999999999999972</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (24th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.50069444444444444</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.53125</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F5" si="0">COUNT(B3:E3)</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.1000000000000005</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.2499999999999991</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.35</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (25th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54236111111111107</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.1</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.25</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (26th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.52013888888888893</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.55069444444444449</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.5666666666666682</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>2.7833333333333314</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (27th)</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="30">
-        <f>IF(G6 = 8, 4, IF(G6 = 4, 2, COUNT(B6:E6)))</f>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>8</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>40.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-0.39999999999999858</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="75" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,28 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E235E6AF-351E-40B5-9C14-19EFDEEE7331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629C2528-037B-465F-931E-1829F9187684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1245" yWindow="570" windowWidth="28800" windowHeight="16680" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="3420" yWindow="555" windowWidth="28800" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260427" sheetId="17" r:id="rId1"/>
-    <sheet name="20260420" sheetId="16" r:id="rId2"/>
-    <sheet name="20260413" sheetId="15" r:id="rId3"/>
-    <sheet name="20260408" sheetId="14" r:id="rId4"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId5"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId6"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId7"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId8"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId10"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId11"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId12"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId13"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId14"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId15"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId16"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId17"/>
+    <sheet name="20260504" sheetId="18" r:id="rId1"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId2"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId3"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId4"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId5"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId6"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId7"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId8"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId9"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId10"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId11"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId12"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId13"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId14"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId15"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId16"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId17"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -74,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -617,7 +618,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="157">
+  <dxfs count="168">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1539,6 +1540,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2412,7 +2520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2432,7 +2540,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>04/27/2026</v>
+        <v>05/04/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2471,7 +2579,7 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (27th)</v>
+        <v>Mon (4th)</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2507,7 +2615,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (28th)</v>
+        <v>Tue (5th)</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2542,7 +2650,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (29th)</v>
+        <v>Wed (6th)</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2577,7 +2685,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (30th)</v>
+        <v>Thu (7th)</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2612,7 +2720,7 @@
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (1st)</v>
+        <v>Fri (8th)</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2774,6 +2882,399 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>03/02/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (2nd)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>6.3333333333333348</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.166666666666667</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.5000000000000018</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>34.999999999999872</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-31.000000000000107</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (3rd)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53888888888888886</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.2666666666666666</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (4th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.4499999999999993</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.916666666666667</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (5th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.48819444444444443</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.8000000000000007</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.549999999999998</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>44.000000000000085</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (6th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.45763888888888887</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.48819444444444443</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>4.0666666666666664</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>4.2833333333333332</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.93333333333333</v>
+      </c>
+      <c r="K7" s="33">
+        <f>((60*5) - SUM(K2:K6)) / 60</f>
+        <v>1.4833333333333338</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.93333333333333</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.93333333333333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="83" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="81" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="79" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="77" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3149,7 +3650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3531,7 +4032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3913,7 +4414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4293,7 +4794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4643,7 +5144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4993,7 +5494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5343,7 +5844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5694,6 +6195,408 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>04/27/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (27th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.51111111111111107</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.35</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.9833333333333334</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (28th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.56388888888888888</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.8833333333333337</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.4666666666666659</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (29th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>4.9000000000000012</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (30th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.56458333333333333</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.59513888888888888</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>6.6333333333333337</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>1.7166666666666659</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (1st)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.29097222222222224</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>4.8333333333333339</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.2833333333333314</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-17.999999999999886</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.666666666666664</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.3166666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.6666666666666643</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.6666666666666643</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="167" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="166" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="165" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="164" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="163" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="161" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="158" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="157" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6095,7 +6998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6497,7 +7400,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6900,7 +7803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7303,7 +8206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7706,7 +8609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8101,7 +9004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8496,397 +9399,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>03/02/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (2nd)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.57638888888888884</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>6.3333333333333348</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.166666666666667</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.5000000000000018</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>34.999999999999872</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-31.000000000000107</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (3rd)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.50763888888888886</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.53888888888888886</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66805555555555551</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.2666666666666666</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.0999999999999996</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (4th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.51527777777777772</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.4499999999999993</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.916666666666667</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (5th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.48819444444444443</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.51875000000000004</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>4.8000000000000007</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.549999999999998</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>44.000000000000085</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (6th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.45763888888888887</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.48819444444444443</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>4.0666666666666664</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>4.2833333333333332</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.93333333333333</v>
-      </c>
-      <c r="K7" s="33">
-        <f>((60*5) - SUM(K2:K6)) / 60</f>
-        <v>1.4833333333333338</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.93333333333333</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.93333333333333</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="83" priority="1" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="2" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="81" priority="6" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="7" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="79" priority="8" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="9" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="77" priority="3" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="4" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="5" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629C2528-037B-465F-931E-1829F9187684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178052A6-35A6-40A8-B8C6-609B08B9049C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3420" yWindow="555" windowWidth="28800" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
@@ -648,6 +648,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -658,6 +668,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -687,6 +707,23 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -698,6 +735,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -708,6 +755,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -717,6 +774,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -728,6 +792,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -738,6 +822,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -862,6 +956,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -872,6 +976,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -929,6 +1043,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -939,6 +1063,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -996,6 +1130,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1006,6 +1150,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1371,175 +1525,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2581,26 +2581,30 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Mon (4th)</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K2" s="13" t="str">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
@@ -2759,7 +2763,7 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
@@ -2775,7 +2779,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>40</v>
+        <v>30.916666666666664</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2834,45 +2838,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="167" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="166" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="165" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="164" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="163" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="162" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="161" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="160" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="158" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="157" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3235,37 +3239,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="83" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="81" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="79" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="77" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3611,37 +3615,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="74" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="72" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="70" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="68" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3993,37 +3997,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="63" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4375,37 +4379,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="56" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="52" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4755,37 +4759,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="45" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="43" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5113,29 +5117,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="36" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5463,29 +5467,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="31" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="29" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5813,29 +5817,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6163,29 +6167,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6549,45 +6553,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="167" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="156" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="155" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="165" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="154" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="153" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="163" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="152" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="151" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="161" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="150" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="149" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="147" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="146" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6951,45 +6955,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="156" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="145" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="144" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="154" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="143" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="142" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="152" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="141" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="140" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="150" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="139" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="138" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="148" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="136" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="135" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7353,45 +7357,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="145" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="143" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="141" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="139" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="137" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7756,45 +7760,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8159,45 +8163,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8562,45 +8566,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="100" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="97" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="96" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="94" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8965,37 +8969,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="101" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="99" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="97" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="95" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9362,37 +9366,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="92" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="90" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="88" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="86" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178052A6-35A6-40A8-B8C6-609B08B9049C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F59425-DD39-43FE-8997-E17EA0E08051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="555" windowWidth="28800" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="3495" yWindow="495" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260504" sheetId="18" r:id="rId1"/>
@@ -2584,35 +2584,39 @@
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="8">
+        <v>0.51944444444444449</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5493055555555556</v>
+      </c>
       <c r="E2" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>5.5500000000000016</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>16</v>
+        <v>2.8166666666666647</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K2" s="13" t="str">
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-23.000000000000028</v>
       </c>
       <c r="M2" s="15"/>
     </row>
@@ -2621,34 +2625,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Tue (5th)</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.51111111111111107</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>0</v>
+        <v>2.9833333333333334</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -2656,34 +2668,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Wed (6th)</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>5.2666666666666666</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -2691,34 +2711,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (7th)</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49791666666666667</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.0333333333333341</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="13" t="str">
+        <v>8.2333333333333343</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>50.999999999999979</v>
+      </c>
+      <c r="L5" s="14">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>-15.000000000000057</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -2726,15 +2754,17 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Fri (8th)</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="31"/>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="10"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>8</v>
+      </c>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
         <v>0</v>
@@ -2745,7 +2775,7 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K6" s="13" t="str">
         <f t="shared" si="4"/>
@@ -2763,11 +2793,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>9.0833333333333339</v>
+        <v>41.283333333333331</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>0</v>
+        <v>1.9500000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2779,7 +2809,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>30.916666666666664</v>
+        <v>-1.2833333333333314</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2787,9 +2817,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25" t="str">
+      <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>-</v>
+        <v>1.2833333333333314</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,29 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F59425-DD39-43FE-8997-E17EA0E08051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D47C31-735E-434A-99BC-210CDBE1973E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3495" yWindow="495" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="1200" yWindow="420" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260504" sheetId="18" r:id="rId1"/>
-    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId2"/>
-    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId3"/>
-    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId4"/>
-    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId5"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId6"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId7"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId8"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId9"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId10"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId11"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId12"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId13"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId14"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId15"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId16"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId17"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId18"/>
+    <sheet name="20260511" sheetId="19" r:id="rId1"/>
+    <sheet name="20260504" sheetId="18" r:id="rId2"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId3"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId4"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId5"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId6"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId7"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId8"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId9"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId11"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId12"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId13"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId14"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId15"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId16"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId17"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId18"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -618,7 +619,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="168">
+  <dxfs count="179">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1433,6 +1434,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2520,7 +2628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2540,7 +2648,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>05/04/2026</v>
+        <v>05/11/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2579,16 +2687,16 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (4th)</v>
+        <v>Mon (11th)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C2" s="8">
-        <v>0.51944444444444449</v>
+        <v>0.49236111111111114</v>
       </c>
       <c r="D2" s="8">
-        <v>0.5493055555555556</v>
+        <v>0.5229166666666667</v>
       </c>
       <c r="E2" s="9">
         <v>0.66666666666666663</v>
@@ -2600,171 +2708,145 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>5.5500000000000016</v>
+        <v>4.9000000000000012</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>2.8166666666666647</v>
+        <v>3.4499999999999984</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>8.3666666666666671</v>
+        <v>8.35</v>
       </c>
       <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
+        <v>44</v>
       </c>
       <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
+        <v>-21.999999999999979</v>
       </c>
       <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (5th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.51111111111111107</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.54236111111111107</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Tue (12th)</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>2.9833333333333334</v>
+        <v>0</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K3" s="13">
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="str">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L3" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
+        <v>-</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (6th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.50763888888888886</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Wed (13th)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.2666666666666666</v>
+        <v>0</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>3.083333333333333</v>
+        <v>0</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L4" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (7th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49791666666666667</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Thu (14th)</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>5.0333333333333341</v>
+        <v>0</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>3.1999999999999993</v>
+        <v>0</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>8.2333333333333343</v>
-      </c>
-      <c r="K5" s="13">
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
-        <v>50.999999999999979</v>
-      </c>
-      <c r="L5" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
         <f t="shared" si="5"/>
-        <v>-15.000000000000057</v>
+        <v>-</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (8th)</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="31"/>
+        <v>Fri (15th)</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
         <v>0</v>
@@ -2775,7 +2857,7 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K6" s="13" t="str">
         <f t="shared" si="4"/>
@@ -2793,11 +2875,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>41.283333333333331</v>
+        <v>8.35</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.9500000000000004</v>
+        <v>4.2666666666666666</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2809,7 +2891,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>-1.2833333333333314</v>
+        <v>31.65</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2817,9 +2899,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="25" t="str">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.2833333333333314</v>
+        <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -2868,45 +2950,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="167" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="178" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="177" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="165" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="176" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="175" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="163" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="174" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="173" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="161" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="172" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="171" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="169" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="168" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2916,6 +2998,403 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>03/09/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (9th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.5833333333333339</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.6333333333333337</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.2166666666666686</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>51.999999999999893</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-14.000000000000114</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (10th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.7666666666666648</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (11th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54027777777777775</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5708333333333333</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.05</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (12th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49791666666666667</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.0166666666666675</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (13th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50208333333333333</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53263888888888888</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.1333333333333337</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.2166666666666659</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.583333333333336</v>
+      </c>
+      <c r="K7" s="33">
+        <f>((60*5) - SUM(K2:K6)) / 60</f>
+        <v>1.1666666666666685</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.5833333333333357</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.5833333333333357</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3308,7 +3787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3684,7 +4163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4066,7 +4545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4448,7 +4927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4828,7 +5307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5178,7 +5657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5528,7 +6007,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5878,7 +6357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6229,6 +6708,402 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>05/04/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (4th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.51944444444444449</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5493055555555556</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.5500000000000016</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.8166666666666647</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (5th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.51111111111111107</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.35</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.9833333333333334</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (6th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.2666666666666666</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>3.083333333333333</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (7th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49791666666666667</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.0333333333333341</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1999999999999993</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.2333333333333343</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>50.999999999999979</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-15.000000000000057</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (8th)</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>8</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.283333333333331</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.9500000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.2833333333333314</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.2833333333333314</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="167" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="166" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="165" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="164" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="163" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="161" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="158" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="157" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6630,7 +7505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7032,7 +7907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7434,7 +8309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7837,7 +8712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8240,7 +9115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8643,7 +9518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -9036,401 +9911,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>03/09/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (9th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.51527777777777772</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.5833333333333339</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.6333333333333337</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.2166666666666686</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>51.999999999999893</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-14.000000000000114</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (10th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66736111111111107</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.7666666666666648</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.35</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (11th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54027777777777775</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.5708333333333333</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.05</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (12th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28888888888888886</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49791666666666667</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28">
-        <v>1</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.0166666666666675</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3166666666666664</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-19.999999999999986</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (13th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.50208333333333333</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.53263888888888888</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.1333333333333337</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3.2166666666666659</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.583333333333336</v>
-      </c>
-      <c r="K7" s="33">
-        <f>((60*5) - SUM(K2:K6)) / 60</f>
-        <v>1.1666666666666685</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.5833333333333357</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.5833333333333357</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -1,37 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D47C31-735E-434A-99BC-210CDBE1973E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA9AAD8-5D3D-4919-BC88-F85B57FDD133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1200" yWindow="420" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260511" sheetId="19" r:id="rId1"/>
-    <sheet name="20260504" sheetId="18" r:id="rId2"/>
-    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId3"/>
-    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId4"/>
-    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId5"/>
-    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId6"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId7"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId8"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId9"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId11"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId12"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId13"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId14"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId15"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId16"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId17"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId18"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId19"/>
+    <sheet name="20260518" sheetId="20" r:id="rId1"/>
+    <sheet name="20260511" sheetId="19" r:id="rId2"/>
+    <sheet name="20260504" sheetId="18" r:id="rId3"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId4"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId5"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId6"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId7"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId8"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId9"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId10"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId11"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId12"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId13"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId14"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId15"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId16"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId17"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId18"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId19"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -76,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -619,7 +620,114 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="179">
+  <dxfs count="190">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2628,7 +2736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147CAD13-550A-47AC-814D-87BFC7C1D749}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2648,7 +2756,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>05/11/2026</v>
+        <v>05/18/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2687,51 +2795,43 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (11th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49236111111111114</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Mon (18th)</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>4.9000000000000012</v>
+        <v>0</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>3.4499999999999984</v>
+        <v>0</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>8.35</v>
-      </c>
-      <c r="K2" s="13">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13" t="str">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L2" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
+        <v>-</v>
       </c>
       <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (12th)</v>
+        <v>Tue (19th)</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2766,7 +2866,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (13th)</v>
+        <v>Wed (20th)</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2801,7 +2901,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (14th)</v>
+        <v>Thu (21st)</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2836,7 +2936,7 @@
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (15th)</v>
+        <v>Fri (22nd)</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2875,11 +2975,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>4.2666666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2891,7 +2991,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>31.65</v>
+        <v>40</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2950,45 +3050,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="178" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="176" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="174" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="172" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="170" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2998,6 +3098,401 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>03/16/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (16th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.53263888888888888</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.1166666666666671</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.2166666666666659</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (17th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53263888888888888</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.2166666666666659</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>46</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (18th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.61041666666666672</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>7.0000000000000018</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.3499999999999979</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (19th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.25</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.083333333333333</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (20th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.25</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.083333333333333</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.666666666666657</v>
+      </c>
+      <c r="K7" s="33">
+        <f>((60*5) - SUM(K2:K6)) / 60</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.6666666666666572</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.6666666666666572</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="101" priority="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="2" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="99" priority="6" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="7" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="97" priority="8" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="9" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="95" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="4" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="5" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3355,37 +3850,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="88" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="87" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="84" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3394,7 +3889,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3748,37 +4243,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="79" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="78" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="75" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3787,7 +4282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4124,37 +4619,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="66" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4163,7 +4658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4506,37 +5001,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="57" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4545,7 +5040,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4888,37 +5383,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="51" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4927,7 +5422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5268,37 +5763,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5307,7 +5802,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5626,29 +6121,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5657,7 +6152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5976,29 +6471,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6007,7 +6502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6326,29 +6821,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6357,7 +6852,409 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>05/11/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (11th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9000000000000012</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (12th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.7500000000000009</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.5999999999999988</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (13th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.53402777777777777</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>3.1833333333333327</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (14th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.55625000000000002</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>6.4333333333333345</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>1.9166666666666652</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (15th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52986111111111112</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.56041666666666667</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.8000000000000007</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>2.5499999999999989</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.75</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.75</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="189" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="188" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="187" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="185" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="183" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="182" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="181" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="179" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6676,29 +7573,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6707,7 +7604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7056,45 +7953,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="167" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="178" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="177" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="165" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="176" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="175" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="163" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="174" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="173" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="161" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="172" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="171" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="169" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="168" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7103,7 +8000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7458,45 +8355,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="156" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="167" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="166" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="154" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="165" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="164" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="152" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="163" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="162" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="150" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="161" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="160" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="148" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="158" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="157" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7505,7 +8402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7860,45 +8757,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="145" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="156" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="155" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="143" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="154" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="153" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="141" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="152" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="151" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="139" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="150" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="149" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="137" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="147" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="146" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7907,7 +8804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8262,45 +9159,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="145" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="144" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="143" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="142" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="141" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="140" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="139" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="138" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="136" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="135" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8309,7 +9206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8665,45 +9562,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8712,7 +9609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -9068,45 +9965,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9115,7 +10012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -9471,440 +10368,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="101" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="99" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="97" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="93" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>03/16/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (16th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.50138888888888888</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.53263888888888888</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.1166666666666671</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.2166666666666659</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (17th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.50069444444444444</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.53263888888888888</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.1000000000000005</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.2166666666666659</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3166666666666664</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>46</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-19.999999999999986</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (18th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.57986111111111116</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.61041666666666672</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>7.0000000000000018</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.3499999999999979</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (19th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50694444444444442</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.25</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.083333333333333</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (20th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.50694444444444442</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.25</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3.083333333333333</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.666666666666657</v>
-      </c>
-      <c r="K7" s="33">
-        <f>((60*5) - SUM(K2:K6)) / 60</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.6666666666666572</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.6666666666666572</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA9AAD8-5D3D-4919-BC88-F85B57FDD133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D99C79-FA34-4F7C-9014-1285A2E192EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="420" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="2445" yWindow="930" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260518" sheetId="20" r:id="rId1"/>
@@ -650,6 +650,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -660,6 +670,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -689,6 +709,23 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -700,6 +737,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -710,6 +757,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -719,6 +776,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -730,6 +794,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -740,6 +824,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -864,6 +958,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -874,6 +978,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -931,6 +1045,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -941,6 +1065,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -998,6 +1132,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1008,6 +1152,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1373,175 +1527,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2797,34 +2797,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Mon (18th)</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.54305555555555551</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>0</v>
+        <v>5.3666666666666663</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>0</v>
+        <v>2.9666666666666668</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
       <c r="M2" s="15"/>
     </row>
@@ -2833,34 +2841,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Tue (19th)</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57916666666666672</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>0</v>
+        <v>6.2500000000000018</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>0</v>
+        <v>2.0999999999999979</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -2868,34 +2884,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Wed (20th)</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.5131944444444444</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.54374999999999996</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -2903,34 +2927,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (21st)</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.60902777777777772</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.0000000000000018</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.3833333333333337</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="13" t="str">
+        <v>8.3833333333333364</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>41.999999999999851</v>
+      </c>
+      <c r="L5" s="14">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>-24.000000000000185</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -2938,15 +2970,17 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Fri (22nd)</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="31"/>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="10"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>8</v>
+      </c>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
         <v>0</v>
@@ -2957,7 +2991,7 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K6" s="13" t="str">
         <f t="shared" si="4"/>
@@ -2975,11 +3009,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>0</v>
+        <v>41.416666666666671</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>0</v>
+        <v>2.0833333333333357</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2991,7 +3025,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>40</v>
+        <v>-1.4166666666666714</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -2999,9 +3033,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25" t="str">
+      <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>-</v>
+        <v>1.4166666666666714</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -3050,45 +3084,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="189" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="188" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="187" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="186" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="185" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="184" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="183" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="182" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="181" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="180" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="179" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3453,37 +3487,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="101" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="99" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="87" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="97" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="95" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3850,37 +3884,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="92" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="90" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="88" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="86" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4243,37 +4277,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="83" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="81" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="69" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="79" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="77" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4619,37 +4653,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="74" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="72" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="70" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="68" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5001,37 +5035,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="63" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5383,37 +5417,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="56" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="52" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5763,37 +5797,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="45" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="43" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="9" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6121,29 +6155,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="36" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6471,29 +6505,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="31" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="29" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6821,29 +6855,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7207,45 +7241,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="189" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="178" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="188" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="177" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="187" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="176" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="175" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="185" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="174" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="173" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="183" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="172" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="182" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="171" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="181" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="169" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="168" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7573,29 +7607,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7953,45 +7987,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="178" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="167" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="166" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="176" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="165" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="164" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="174" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="163" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="162" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="172" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="161" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="160" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="170" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="158" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="157" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8355,45 +8389,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="167" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="156" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="155" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="165" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="154" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="153" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="163" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="152" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="151" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="161" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="150" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="149" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="147" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="146" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8757,45 +8791,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="156" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="145" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="144" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="154" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="143" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="142" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="152" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="141" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="140" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="150" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="139" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="138" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="148" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="136" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="135" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9159,45 +9193,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="145" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="143" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="141" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="139" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="137" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9562,45 +9596,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="134" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="132" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="130" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9965,45 +9999,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10368,45 +10402,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="100" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="97" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="96" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="94" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -1,38 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D99C79-FA34-4F7C-9014-1285A2E192EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DB6F81-4BAA-40D5-91AD-5236EBB2DA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2445" yWindow="930" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="2715" yWindow="915" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260518" sheetId="20" r:id="rId1"/>
-    <sheet name="20260511" sheetId="19" r:id="rId2"/>
-    <sheet name="20260504" sheetId="18" r:id="rId3"/>
-    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId4"/>
-    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId5"/>
-    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId6"/>
-    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId7"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId8"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId9"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId10"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId11"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId12"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId13"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId14"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId15"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId16"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId17"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId18"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId19"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId20"/>
+    <sheet name="20260526" sheetId="21" r:id="rId1"/>
+    <sheet name="20260518" sheetId="20" r:id="rId2"/>
+    <sheet name="20260511" sheetId="19" r:id="rId3"/>
+    <sheet name="20260504" sheetId="18" r:id="rId4"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId5"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId6"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId7"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId8"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId9"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId10"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId12"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId13"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId14"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId15"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId16"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId17"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId18"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId19"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId20"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -620,7 +621,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="190">
+  <dxfs count="201">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1435,6 +1436,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2736,7 +2844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147CAD13-550A-47AC-814D-87BFC7C1D749}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADA2EDE-7873-4984-BD8B-6BE6DA51A055}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2756,7 +2864,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>05/18/2026</v>
+        <v>05/26/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2795,60 +2903,62 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (18th)</v>
+        <v>Tue (26th)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C2" s="8">
-        <v>0.51180555555555551</v>
+        <v>0.51527777777777772</v>
       </c>
       <c r="D2" s="8">
-        <v>0.54305555555555551</v>
+        <v>0.53749999999999998</v>
       </c>
       <c r="E2" s="9">
-        <v>0.66666666666666663</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
         <v>4</v>
       </c>
-      <c r="G2" s="10"/>
+      <c r="G2" s="10">
+        <v>0.5</v>
+      </c>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>5.3666666666666663</v>
+        <v>5.4499999999999993</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>2.9666666666666668</v>
+        <v>2.6000000000000014</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>8.3333333333333321</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>45</v>
+        <v>32.000000000000043</v>
       </c>
       <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
+        <v>-34.000000000000043</v>
       </c>
       <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (19th)</v>
+        <v>Wed (27th)</v>
       </c>
       <c r="B3" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C3" s="8">
-        <v>0.54861111111111116</v>
+        <v>0.50347222222222221</v>
       </c>
       <c r="D3" s="8">
-        <v>0.57916666666666672</v>
+        <v>0.53402777777777777</v>
       </c>
       <c r="E3" s="9">
         <v>0.66666666666666663</v>
@@ -2860,11 +2970,11 @@
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>6.2500000000000018</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>2.0999999999999979</v>
+        <v>3.1833333333333327</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
@@ -2882,105 +2992,87 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (20th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.5131944444444444</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.54374999999999996</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Thu (28th)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.3999999999999995</v>
+        <v>0</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L4" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (21st)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.57986111111111116</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.60902777777777772</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Fri (29th)</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>7.0000000000000018</v>
+        <v>0</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>1.3833333333333337</v>
+        <v>0</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>8.3833333333333364</v>
-      </c>
-      <c r="K5" s="13">
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
-        <v>41.999999999999851</v>
-      </c>
-      <c r="L5" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
         <f t="shared" si="5"/>
-        <v>-24.000000000000185</v>
+        <v>-</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (22nd)</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="31"/>
+        <v>Sat (30th)</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
         <v>0</v>
@@ -2991,7 +3083,7 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K6" s="13" t="str">
         <f t="shared" si="4"/>
@@ -3009,11 +3101,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>41.416666666666671</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.0833333333333357</v>
+        <v>3.7333333333333325</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -3025,7 +3117,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>-1.4166666666666714</v>
+        <v>23.1</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -3033,9 +3125,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="25" t="str">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.4166666666666714</v>
+        <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -3084,45 +3176,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="189" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="200" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="188" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="199" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="187" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="198" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="197" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="185" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="196" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="195" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="183" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="194" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="182" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="193" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="181" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="192" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="191" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="190" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3132,6 +3224,409 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>03/23/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (23rd)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.56736111111111109</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.95</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.3833333333333329</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (24th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53055555555555556</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.0833333333333339</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.2666666666666657</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (25th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.3666666666666663</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.9833333333333334</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (26th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.3833333333333329</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>2.9833333333333334</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (27th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.5666666666666682</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>2.7499999999999982</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.716666666666669</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.7166666666666686</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.7166666666666686</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="101" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="99" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="97" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="93" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="92" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3526,7 +4021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3923,7 +4418,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4316,7 +4811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4692,7 +5187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5074,7 +5569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5456,7 +5951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5836,7 +6331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6186,7 +6681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6536,7 +7031,403 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147CAD13-550A-47AC-814D-87BFC7C1D749}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>05/18/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (18th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.54305555555555551</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.3666666666666663</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.9666666666666668</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (19th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57916666666666672</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.2500000000000018</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.0999999999999979</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (20th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.5131944444444444</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.54374999999999996</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.3999999999999995</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.95</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (21st)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.60902777777777772</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>7.0000000000000018</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>1.3833333333333337</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3833333333333364</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>41.999999999999851</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-24.000000000000185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (22nd)</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>8</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.416666666666671</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>2.0833333333333357</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.4166666666666714</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.4166666666666714</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="189" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="188" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="187" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="185" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="183" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="182" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="181" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="179" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6886,7 +7777,357 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4333333333333318</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.2833333333333332</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>3.466666666666665</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44.000000000000085</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6166666666666654</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.7999999999999972</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7288,357 +8529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49375000000000002</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4333333333333318</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57152777777777775</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.2833333333333332</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52222222222222225</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>3.466666666666665</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44.000000000000085</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3999999999999986</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.6166666666666654</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.7999999999999972</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8034,7 +8925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8436,7 +9327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8838,7 +9729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -9240,7 +10131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -9643,7 +10534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -10044,407 +10935,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>03/23/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (23rd)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.53611111111111109</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.56736111111111109</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.95</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.3833333333333329</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (24th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.53055555555555556</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.0833333333333339</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.2666666666666657</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.35</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (25th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.51180555555555551</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.54236111111111107</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.3666666666666663</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.9833333333333334</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (26th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.51249999999999996</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.54236111111111107</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.3833333333333329</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>2.9833333333333334</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (27th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52013888888888893</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.5666666666666682</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>2.7499999999999982</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3166666666666664</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>46</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-19.999999999999986</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.716666666666669</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.7166666666666686</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.7166666666666686</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="101" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="99" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="97" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="93" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,32 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DB6F81-4BAA-40D5-91AD-5236EBB2DA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A6E461-547B-4CFC-BA13-07389E981787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="915" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="3060" yWindow="1260" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260526" sheetId="21" r:id="rId1"/>
-    <sheet name="20260518" sheetId="20" r:id="rId2"/>
-    <sheet name="20260511" sheetId="19" r:id="rId3"/>
-    <sheet name="20260504" sheetId="18" r:id="rId4"/>
-    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId5"/>
-    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId6"/>
-    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId7"/>
-    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId8"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId9"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId10"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId12"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId13"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId14"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId15"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId16"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId17"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId18"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId19"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId20"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId21"/>
+    <sheet name="20260601" sheetId="22" r:id="rId1"/>
+    <sheet name="20260525" sheetId="21" r:id="rId2"/>
+    <sheet name="20260518" sheetId="20" r:id="rId3"/>
+    <sheet name="20260511" sheetId="19" r:id="rId4"/>
+    <sheet name="20260504" sheetId="18" r:id="rId5"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId6"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId7"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId8"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId9"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId10"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId11"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId12"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId13"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId14"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId15"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId16"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId17"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId18"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId19"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId20"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId21"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -78,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -621,7 +622,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="201">
+  <dxfs count="212">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1436,6 +1437,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2844,7 +2952,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADA2EDE-7873-4984-BD8B-6BE6DA51A055}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC499B9-050F-4A63-AD58-B03C062DE40E}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2864,7 +2972,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>05/26/2026</v>
+        <v>06/01/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2903,96 +3011,78 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (26th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.51527777777777772</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.53749999999999998</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.64583333333333337</v>
-      </c>
+        <v>Mon (1st)</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>5.4499999999999993</v>
+        <v>0</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>2.6000000000000014</v>
+        <v>0</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>8.5500000000000007</v>
-      </c>
-      <c r="K2" s="13">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13" t="str">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>32.000000000000043</v>
-      </c>
-      <c r="L2" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-34.000000000000043</v>
+        <v>-</v>
       </c>
       <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (27th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.50347222222222221</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.53402777777777777</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Tue (2nd)</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>5.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>3.1833333333333327</v>
+        <v>0</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.35</v>
-      </c>
-      <c r="K3" s="13">
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="str">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L3" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
+        <v>-</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (28th)</v>
+        <v>Wed (3rd)</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -3027,7 +3117,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (29th)</v>
+        <v>Thu (4th)</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3062,7 +3152,7 @@
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Sat (30th)</v>
+        <v>Fri (5th)</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3101,11 +3191,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>16.899999999999999</v>
+        <v>0</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>3.7333333333333325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -3117,7 +3207,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>23.1</v>
+        <v>40</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -3176,45 +3266,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="200" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="211" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="210" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="198" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="209" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="197" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="208" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="196" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="207" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="206" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="194" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="205" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="204" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="192" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="203" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="191" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="202" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="201" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3224,6 +3314,409 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>03/30/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (30th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.48541666666666666</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.51666666666666672</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.7333333333333343</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.5999999999999979</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45.000000000000078</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (31st)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53680555555555554</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.2166666666666668</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.1166666666666663</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (1st)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.57708333333333328</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.1999999999999993</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.166666666666667</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (2nd)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50902777777777775</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.5395833333333333</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.3</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.05</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (3rd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.49583333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>4.9833333333333343</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.716666666666669</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.2833333333333319</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.7166666666666686</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.7166666666666686</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3626,7 +4119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4021,7 +4514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4418,7 +4911,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4811,7 +5304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5187,7 +5680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5569,7 +6062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5951,7 +6444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6331,7 +6824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6681,7 +7174,405 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADA2EDE-7873-4984-BD8B-6BE6DA51A055}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>05/25/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (25th)</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>8</v>
+      </c>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8</v>
+      </c>
+      <c r="K2" s="13" t="str">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (26th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.4499999999999993</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.6000000000000014</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>32.000000000000043</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-34.000000000000043</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (27th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.53402777777777777</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>3.1833333333333327</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (28th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.2666666666666666</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (29th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50902777777777775</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54027777777777775</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.3</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.0333333333333332</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.599999999999994</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>2.2666666666666657</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.5999999999999943</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.5999999999999943</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="200" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="199" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="198" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="197" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="196" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="195" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="194" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="193" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="192" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="191" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="190" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7031,7 +7922,707 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/12/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (12th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9000000000000012</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.35</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (13th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.366666666666668</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.9833333333333316</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.35</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (14th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.4333333333333327</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (15th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0666666666666664</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-14.99999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (16th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.4499999999999993</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.916666666666667</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.6499999999999986</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4333333333333318</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.2833333333333332</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>3.466666666666665</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44.000000000000085</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6166666666666654</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.7999999999999972</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147CAD13-550A-47AC-814D-87BFC7C1D749}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7427,707 +9018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/12/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (12th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49236111111111114</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9000000000000012</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4499999999999984</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.35</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (13th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.58402777777777781</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.366666666666668</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.9833333333333316</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.35</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (14th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56527777777777777</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.916666666666667</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.4333333333333327</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (15th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50555555555555554</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53611111111111109</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66805555555555551</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>5.0666666666666664</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.2333333333333325</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-14.99999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (16th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.51527777777777772</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.4499999999999993</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.916666666666667</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.6499999999999986</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49375000000000002</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4333333333333318</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57152777777777775</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.2833333333333332</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52222222222222225</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>3.466666666666665</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44.000000000000085</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3999999999999986</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.6166666666666654</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.7999999999999972</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8529,7 +9420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -8925,7 +9816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -9327,7 +10218,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -9729,7 +10620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -10131,7 +11022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -10532,407 +11423,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>03/30/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (30th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.48541666666666666</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.51666666666666672</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.7333333333333343</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.5999999999999979</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>45.000000000000078</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (31st)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.50555555555555554</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.53680555555555554</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.2166666666666668</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.1166666666666663</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (1st)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54652777777777772</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.57708333333333328</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66736111111111107</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.1999999999999993</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.166666666666667</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (2nd)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50902777777777775</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.5395833333333333</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.3</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.05</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (3rd)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.49583333333333335</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>4.9833333333333343</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3.3499999999999988</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.716666666666669</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.2833333333333319</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.7166666666666686</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.7166666666666686</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="112" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="110" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="108" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="104" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A6E461-547B-4CFC-BA13-07389E981787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E018AA-E616-4E3C-B51B-EDE228D116F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="1260" windowWidth="32970" windowHeight="18735" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="1725" yWindow="585" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260601" sheetId="22" r:id="rId1"/>
@@ -3013,34 +3013,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Mon (1st)</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.53125</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>0</v>
+        <v>5.0833333333333339</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>0</v>
+        <v>3.2499999999999991</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
       <c r="M2" s="15"/>
     </row>
@@ -3049,34 +3057,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Tue (2nd)</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.47986111111111113</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.51944444444444449</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>0</v>
+        <v>4.6000000000000014</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>0</v>
+        <v>3.5333333333333314</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.1333333333333329</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>57.000000000000036</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-8.9999999999999716</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -3084,34 +3100,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Wed (3rd)</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="8">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>3.1499999999999995</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.5</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>34.000000000000043</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -3191,11 +3215,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>0</v>
+        <v>24.966666666666665</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>0</v>
+        <v>2.7333333333333325</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -3207,7 +3231,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>40</v>
+        <v>15.033333333333335</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,33 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E018AA-E616-4E3C-B51B-EDE228D116F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B55879-751F-4F0B-A8DC-67291944EBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="585" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="4485" yWindow="1575" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260601" sheetId="22" r:id="rId1"/>
-    <sheet name="20260525" sheetId="21" r:id="rId2"/>
-    <sheet name="20260518" sheetId="20" r:id="rId3"/>
-    <sheet name="20260511" sheetId="19" r:id="rId4"/>
-    <sheet name="20260504" sheetId="18" r:id="rId5"/>
-    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId6"/>
-    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId7"/>
-    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId8"/>
-    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId9"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId10"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId11"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId12"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId13"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId14"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId15"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId16"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId17"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId18"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId19"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId20"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId21"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId22"/>
+    <sheet name="20260608" sheetId="23" r:id="rId1"/>
+    <sheet name="20260601" sheetId="22" r:id="rId2"/>
+    <sheet name="20260525" sheetId="21" r:id="rId3"/>
+    <sheet name="20260518" sheetId="20" r:id="rId4"/>
+    <sheet name="20260511" sheetId="19" r:id="rId5"/>
+    <sheet name="20260504" sheetId="18" r:id="rId6"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId7"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId8"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId9"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId10"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId11"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId13"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId14"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId15"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId16"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId17"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId18"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId19"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId20"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId21"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId22"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -622,7 +623,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="212">
+  <dxfs count="223">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1437,6 +1438,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2952,7 +3060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC499B9-050F-4A63-AD58-B03C062DE40E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F536AF-B26B-4088-9F12-A3C7FDB6B0E0}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2972,7 +3080,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>06/01/2026</v>
+        <v>06/08/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -3011,16 +3119,16 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (1st)</v>
+        <v>Mon (8th)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C2" s="8">
-        <v>0.5</v>
+        <v>0.48888888888888887</v>
       </c>
       <c r="D2" s="8">
-        <v>0.53125</v>
+        <v>0.52013888888888893</v>
       </c>
       <c r="E2" s="9">
         <v>0.66666666666666663</v>
@@ -3032,11 +3140,11 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>5.0833333333333339</v>
+        <v>4.8166666666666664</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>3.2499999999999991</v>
+        <v>3.5166666666666648</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
@@ -3044,7 +3152,7 @@
       </c>
       <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>45</v>
+        <v>45.000000000000078</v>
       </c>
       <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
@@ -3055,16 +3163,16 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (2nd)</v>
+        <v>Tue (9th)</v>
       </c>
       <c r="B3" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C3" s="8">
-        <v>0.47986111111111113</v>
+        <v>0.5</v>
       </c>
       <c r="D3" s="8">
-        <v>0.51944444444444449</v>
+        <v>0.53055555555555556</v>
       </c>
       <c r="E3" s="9">
         <v>0.66666666666666663</v>
@@ -3076,38 +3184,38 @@
       <c r="G3" s="10"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>4.6000000000000014</v>
+        <v>5.0833333333333339</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>3.5333333333333314</v>
+        <v>3.2666666666666657</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.1333333333333329</v>
+        <v>8.35</v>
       </c>
       <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>57.000000000000036</v>
+        <v>44</v>
       </c>
       <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-8.9999999999999716</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (3rd)</v>
+        <v>Wed (10th)</v>
       </c>
       <c r="B4" s="8">
-        <v>0.28888888888888886</v>
+        <v>0.28819444444444442</v>
       </c>
       <c r="C4" s="8">
-        <v>0.51180555555555551</v>
+        <v>0.52013888888888893</v>
       </c>
       <c r="D4" s="8">
-        <v>0.53541666666666665</v>
+        <v>0.55138888888888893</v>
       </c>
       <c r="E4" s="9">
         <v>0.66666666666666663</v>
@@ -3119,93 +3227,109 @@
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.35</v>
+        <v>5.5666666666666682</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>3.1499999999999995</v>
+        <v>2.7666666666666648</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>8.5</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>34.000000000000043</v>
+        <v>45</v>
       </c>
       <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-31</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (4th)</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
+        <v>Thu (11th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.51111111111111107</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.54097222222222219</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.0166666666666666</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="13" t="str">
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>-23.000000000000028</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (5th)</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
+        <v>Fri (12th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>0</v>
+        <v>5.2166666666666668</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.1499999999999995</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="13" t="str">
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K6" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L6" s="14">
         <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-23.000000000000028</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
@@ -3215,11 +3339,11 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>24.966666666666665</v>
+        <v>41.749999999999993</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.7333333333333325</v>
+        <v>1.3333333333333319</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -3231,7 +3355,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>15.033333333333335</v>
+        <v>-1.7499999999999929</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -3239,9 +3363,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25" t="str">
+      <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>-</v>
+        <v>1.7499999999999929</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -3290,45 +3414,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="211" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="222" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="221" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="209" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="220" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="219" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="207" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="218" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="206" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="217" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="205" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="216" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="215" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="203" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="214" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="213" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="212" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3338,6 +3462,409 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>04/08/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (8th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9166666666666679</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4166666666666652</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (9th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (10th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49027777777777776</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.2999999999999972</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>47.000000000000071</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-18.999999999999829</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Sat (11th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>45.000000000000078</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Sun (12th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.49861111111111112</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.0500000000000007</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.2999999999999989</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.666666666666664</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.2499999999999976</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.6666666666666643</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.6666666666666643</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="113" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -3740,7 +4267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4143,7 +4670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4538,7 +5065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -4935,7 +5462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5328,7 +5855,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5704,7 +6231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6086,7 +6613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6468,7 +6995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6848,7 +7375,409 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC499B9-050F-4A63-AD58-B03C062DE40E}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>06/01/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (1st)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.53125</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.0833333333333339</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.2499999999999991</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (2nd)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.47986111111111113</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.51944444444444449</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>4.6000000000000014</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.5333333333333314</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.1333333333333329</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>57.000000000000036</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-8.9999999999999716</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (3rd)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.35</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>3.1499999999999995</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>34.000000000000043</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (4th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50624999999999998</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.2166666666666668</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (5th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.4833333333333316</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666636</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000085</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-22.999999999999815</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.649999999999991</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.2666666666666644</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.6499999999999915</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.6499999999999915</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="211" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="210" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="209" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="208" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="207" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="206" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="205" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="204" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="203" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="202" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="201" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7198,7 +8127,1057 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/19/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (19th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55069444444444449</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.7833333333333314</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (20th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>4.5333333333333332</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.666666666666667</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.999999999999922</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-12.999999999999957</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (21st)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.2902777777777778</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56736111111111109</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.9499999999999993</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.3833333333333329</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (22nd)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.59583333333333333</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999993</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (23rd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.29583333333333334</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.56041666666666667</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.35</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>1.8333333333333321</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.1833333333333318</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-11.999999999999908</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.449999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.4499999999999957</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/12/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (12th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9000000000000012</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.35</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (13th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.366666666666668</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.9833333333333316</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.35</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (14th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>2.4333333333333327</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (15th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.29444444444444445</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.0666666666666664</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-14.99999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (16th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.4499999999999993</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.916666666666667</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.6499999999999986</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>01/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.4333333333333318</v>
+      </c>
+      <c r="I2" s="12">
+        <f>G2 + H2 + F2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="H3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.2833333333333332</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="K3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
+        <v>3.466666666666665</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" si="0"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44.000000000000085</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="2"/>
+        <v>3.3999999999999986</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="4"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6166666666666654</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="K6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUM(I2:I6)</f>
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="H9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="25">
+        <f>40-I7</f>
+        <v>-1.7999999999999972</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADA2EDE-7873-4984-BD8B-6BE6DA51A055}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7596,1057 +9575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/19/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (19th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55069444444444449</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.7833333333333314</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (20th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.48333333333333334</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.51388888888888884</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>4.5333333333333332</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.666666666666667</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.999999999999922</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-12.999999999999957</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (21st)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.2902777777777778</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53819444444444442</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56736111111111109</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.9499999999999993</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.3833333333333329</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>42.000000000000014</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (22nd)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.56597222222222221</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.59583333333333333</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>6.666666666666667</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>1.6999999999999993</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (23rd)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.29583333333333334</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.56041666666666667</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.59027777777777779</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>6.35</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>1.8333333333333321</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.1833333333333318</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-11.999999999999908</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.449999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.4499999999999957</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/12/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (12th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49236111111111114</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9000000000000012</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4499999999999984</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.35</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (13th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.58402777777777781</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.366666666666668</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.9833333333333316</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.35</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (14th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56527777777777777</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>5.916666666666667</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>2.4333333333333327</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (15th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.29444444444444445</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50555555555555554</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53611111111111109</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66805555555555551</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>5.0666666666666664</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.2333333333333325</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-14.99999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (16th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.51527777777777772</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.4499999999999993</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.916666666666667</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.6499999999999986</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="26" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>01/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49375000000000002</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4333333333333318</v>
-      </c>
-      <c r="I2" s="12">
-        <f>G2 + H2 + F2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="J2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - I2) * 60) + 1) &gt; 0, (((8 - I2) * 60) + 1), (((8 - I2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57152777777777775</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="H3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.2833333333333332</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I6" si="0">G3 + H3 + F3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="J3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="K3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - I3) * 60) + 1) &gt; 0, (((8 - I3) * 60) + 1), (((8 - I3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52222222222222225</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G5" si="1">SUM(C4 - B4) * 24</f>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H6" si="2">SUM(E4 - D4) * 24</f>
-        <v>3.466666666666665</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" si="0"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" ref="J4:J6" si="3">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44.000000000000085</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" ref="K4:K5" si="4">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - I4) * 60) + 1) &gt; 0, (((8 - I4) * 60) + 1), (((8 - I4) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10">
-        <f t="shared" si="1"/>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3999999999999986</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K5" s="14">
-        <f t="shared" si="4"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="2"/>
-        <v>2.6166666666666654</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="K6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - I6) * 60) + 1) &gt; 0, (((8 - I6) * 60) + 1), (((8 - I6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="H7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="22">
-        <f>SUM(I2:I6)</f>
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="F9" s="23"/>
-      <c r="H9" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="25">
-        <f>40-I7</f>
-        <v>-1.7999999999999972</v>
-      </c>
-      <c r="J9" s="26"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147CAD13-550A-47AC-814D-87BFC7C1D749}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -9042,7 +9971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -9444,7 +10373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -9840,7 +10769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -10242,7 +11171,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -10644,7 +11573,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -11044,407 +11973,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>04/08/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (8th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49305555555555558</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52430555555555558</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.9166666666666679</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.4166666666666652</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (9th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.3999999999999986</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.35</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (10th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49027777777777776</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>3.4499999999999984</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.2999999999999972</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>47.000000000000071</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-18.999999999999829</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Sat (11th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.4499999999999984</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>45.000000000000078</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Sun (12th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.49861111111111112</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.0500000000000007</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3.2999999999999989</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.666666666666664</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.2499999999999976</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.6666666666666643</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.6666666666666643</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="123" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="121" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="119" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="115" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="6" operator="